--- a/resources/templates/system/transfer_certificate.xlsx
+++ b/resources/templates/system/transfer_certificate.xlsx
@@ -164,44 +164,40 @@
     <t>제1조 (당사자표시) 양도인을 "갑"이라 하고, 양수인을 "을"이라 한다.</t>
   </si>
   <si>
-    <t>제2조 (동시이행 등) ① "갑"은 잔금 수령과 상환으로 소유권이전등록에 필요한 서류와 매매목적물을 "을"에게 인도하기로 한다. 다만,
-       "갑"과 "을"의 합의에 따라 매매금액의 2/3 이상의 상당액을 지급한 경우에는 매매목적물을 인도할 수 있다. ② "을"은 "갑"에게
-       잔금을 지급함과 동시에 소유권이전등록의 절차에 필요한 서류와 등록비용을 자동차매매업자(이하 "매매업자"라 한다)에게 내주어야
-       한다. 다만, 매매업자가 매수할 때에는 그러하지 아니하다. ③ 매매업자는 잔금지급일부터 15일 이내에 자동차소유권 이전등록 신청을
-       하여야 한다.</t>
-  </si>
-  <si>
-    <t>제3조 (공과금 부담) 이 자동차에 대한 제세공과금은 자동차 인도일을 기준으로 하여, 그 기준일까지의 분은 "갑"이 부담하고 기준일
-       다음날부터의 분은 "을"이 부담한다. 다만, 관계 법령에 제세공과금 납부에 관하여 특별한 규정이 있는 경우에는 그에 따른다.</t>
+    <t>제2조 (동시이행 등) ① "갑"은 잔금 수령과 상환으로 소유권이전등록에 필요한 서류와 매매목적물을 "을"에게 인도하기로 한다. 다만, "갑"과 "을"의 합의에 따라 매매금액의 2/3 이상의
+       상당액을 지급한 경우에는 매매목적물을 인도할 수 있다. ② "을"은 "갑"에게 잔금을 지급함과 동시에 소유권이전등록의 절차에 필요한 서류와 등록비용을 자동차매매업자(이하
+       "매매업자"라 한다)에게 내주어야 한다. 다만, 매매업자가 매수할 때에는 그러하지 아니하다. ③ 매매업자는 잔금지급일부터 15일 이내에 자동차소유권 이전등록 신청을 하여야
+       한다.</t>
+  </si>
+  <si>
+    <t>제3조 (공과금 부담) 이 자동차에 대한 제세공과금은 자동차 인도일을 기준으로 하여, 그 기준일까지의 분은 "갑"이 부담하고 기준일 다음날부터의 분은 "을"이 부담한다. 다만, 관계
+       법령에 제세공과금 납부에 관하여 특별한 규정이 있는 경우에는 그에 따른다.</t>
   </si>
   <si>
     <t>제4조 (사고책임) "을"은 이 자동차를 인수한 때부터 발생하는 모든 사고에 대하여 자기를 위하여 운행하는 자로서의 책임을 진다.</t>
   </si>
   <si>
-    <t>제5조 (법률상의 하자책임) ① 자동차 인도일 이전에 발생한 행정처분 또는 이전등록 요건의 불비 등의 하자에 대해서는 "갑"이 그 책임을
-       진다. ② 매매업자는 「자동차관리법」 제58조제1항에 따라 자동차의 성능 · 상태의 점검 내용을 "을"에게 알려야 하고, "을"이
-       원하는 경우 같은 법 제58조의4에 해당하는 자가 자동차 가격을 조사 · 산정한 내용을 알려야 한다.</t>
-  </si>
-  <si>
-    <t>제6조 (해약금 등) ① "갑"이 이 계약을 위반한 경우에는 "갑"은 해약금으로 계약금의 2배액을 "을"에게 배상해야 하며, "을"이 위약한
-       경우에는 "을"은 "갑"에게 계약금의 반환을 요구할 수 없다. 다만, 손해배상의 청구는 방해하지 않는다. ② 제5조제2항에 따라 "갑"이
-       고지한 자동차의 성능 · 상태의 점검내용 중 주행거리, 사고 또는 침수사실이 다르거나, "갑"이 자동차의 성능 · 상태의 점검내용
-       또는 압류 · 저당권의 등록 여부를 거짓으로 고지하거나 고지하지 아니한 경우 "을"은 자동차인도일로부터 30일 이내에 매매계약을
-       해제할 수 있으며, 이 경우 "을"은 자동차를 즉시 "갑"에게 반환하고 "갑"은 자동차의 반환과 동시에 이미 지급받은 매매금액을
-       "을"에게 반환하여야 한다.</t>
-  </si>
-  <si>
-    <t>제7조 (매매업자의 책임) 제5조의 하자에 대해서는 매매업자가 매도인과 동일한 책임을 지며, 시 · 도의 조례가 하자보증금을 예치하도록
-       하는 경우 매수인의 요청이 있을 때에는 그 하자보증금으로 매수인에게 우선 지급해야 한다. 다만, 매매업자는 양도인 또는 그 하자에
-       책임이 있는 자에 대하여 구상권을 행사할 수 있다.</t>
-  </si>
-  <si>
-    <t>제8조 (등록 지체 책임) "갑"과 "을"이 매매업자에게 이전등록의 대행에 필요한 서류 등의 발급 또는 권한의 위임을 한 후 매매업자가
-       이전등록 신청을 대행하지 않을 때에는 이에 대한 모든 책임은 매매업자가 진다.</t>
-  </si>
-  <si>
-    <t>제9조 (할부승계 특약) "갑"이 자동차를 할부로 구입하여 할부금을 다 내지 않은 상태에서 "을"에게 양도하는 경우에는 나머지 할부금을
-       "을"이 승계하여 부담할 것인지의 여부를 특약사항란에 적어야 한다.</t>
+    <t>제5조 (법률상의 하자책임) ① 자동차 인도일 이전에 발생한 행정처분 또는 이전등록 요건의 불비 등의 하자에 대해서는 "갑"이 그 책임을 진다. ② 매매업자는 「자동차관리법」
+       제58조제1항에 따라 자동차의 성능 · 상태의 점검 내용을 "을"에게 알려야 하고, "을"이 원하는 경우 같은 법 제58조의4에 해당하는 자가 자동차 가격을 조사 · 산정한 내용을
+       알려야 한다.</t>
+  </si>
+  <si>
+    <t>제6조 (해약금 등) ① "갑"이 이 계약을 위반한 경우에는 "갑"은 해약금으로 계약금의 2배액을 "을"에게 배상해야 하며, "을"이 위약한 경우에는 "을"은 "갑"에게 계약금의 반환을 요구할
+       수 없다. 다만, 손해배상의 청구는 방해하지 않는다. ② 제5조제2항에 따라 "갑"이 고지한 자동차의 성능 · 상태의 점검내용 중 주행거리, 사고 또는 침수사실이 다르거나, "갑"이
+       자동차의 성능 · 상태의 점검내용 또는 압류 · 저당권의 등록 여부를 거짓으로 고지하거나 고지하지 아니한 경우 "을"은 자동차인도일로부터 30일 이내에 매매계약을 해제할 수
+       있으며, 이 경우 "을"은 자동차를 즉시 "갑"에게 반환하고 "갑"은 자동차의 반환과 동시에 이미 지급받은 매매금액을 "을"에게 반환하여야 한다.</t>
+  </si>
+  <si>
+    <t>제7조 (매매업자의 책임) 제5조의 하자에 대해서는 매매업자가 매도인과 동일한 책임을 지며, 시 · 도의 조례가 하자보증금을 예치하도록 하는 경우 매수인의 요청이 있을 때에는 그
+       하자보증금으로 매수인에게 우선 지급해야 한다. 다만, 매매업자는 양도인 또는 그 하자에 책임이 있는 자에 대하여 구상권을 행사할 수 있다.</t>
+  </si>
+  <si>
+    <t>제8조 (등록 지체 책임) "갑"과 "을"이 매매업자에게 이전등록의 대행에 필요한 서류 등의 발급 또는 권한의 위임을 한 후 매매업자가 이전등록 신청을 대행하지 않을 때에는 이에 대한
+       모든 책임은 매매업자가 진다.</t>
+  </si>
+  <si>
+    <t>제9조 (할부승계 특약) "갑"이 자동차를 할부로 구입하여 할부금을 다 내지 않은 상태에서 "을"에게 양도하는 경우에는 나머지 할부금을 "을"이 승계하여 부담할 것인지의 여부를
+       특약사항란에 적어야 한다.</t>
   </si>
   <si>
     <t>제10조 (계약서) 이 계약서는 년 월 일 4통 작성하여 "갑"이 1통, "을"이 1통, 등록절차를 대행하는 매매업자가 2통씩을 각각 지닌다.</t>
@@ -255,9 +251,8 @@
     <t>성능 책임 보험료</t>
   </si>
   <si>
-    <t>「자동차등록규칙」 제33조제2항제2호에 따라
-위의 중고자동차매매계약서 기재내용과 같이
-양도하였음을 증명합니다.</t>
+    <t>「자동차등록규칙」 제33조제2항제2호에 따라 위의
+중고자동차매매계약서 기재내용과 같이 양도하였음을 증명합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">        년                 월                 일       </t>
@@ -269,12 +264,10 @@
     <t xml:space="preserve">  양수인</t>
   </si>
   <si>
-    <t>(유의사항) 1. 이 양도증명서는 「자동차관리법」에 따라 자동차매매업의 등록을 한 자만이 사용할 수 있습니다. 2. 매매업자는 반드시
-              직인을 찍어야 합니다. 3. 자동차매매사업조합의 중고자동차 제시 또는 매도신고번호를 적어야 합니다. 4. 이 양도증명서를
-              작성할 때 매매대상 중고자동차의 배출가스저감장치 자기부담금의 납부 여부를 확인하여 뜻하지 않은 손해를 입지 않도록
-              하시기 바랍니다. 5. 자동차정비, 검사, 주행거리 이력, 자동차세 납부 여부, 압류내역 및 배출가스저감장치 자기부담금
-              납부내역 등 자동차토탈이력정보는 국토교통부에서 제공하는 스마트폰용 어플("마이카정보") 또는
-              자동차민원대국민포털(www.ecar.go.kr)에서 조회가 가능하므로 확인 바랍니다.</t>
+    <t>(유의사항) 1. 이 양도증명서는 「자동차관리법」에 따라 자동차매매업의 등록을 한 자만이 사용할 수 있습니다. 2. 매매업자는 반드시 직인을 찍어야 합니다. 3. 자동차매매사업조합의
+              중고자동차 제시 또는 매도신고번호를 적어야 합니다. 4. 이 양도증명서를 작성할 때 매매대상 중고자동차의 배출가스저감장치 자기부담금의 납부 여부를 확인하여 뜻하지
+              않은 손해를 입지 않도록 하시기 바랍니다. 5. 자동차정비, 검사, 주행거리 이력, 자동차세 납부 여부, 압류내역 및 배출가스저감장치 자기부담금 납부내역 등
+              자동차토탈이력정보는 국토교통부에서 제공하는 스마트폰용 어플("마이카정보") 또는 자동차민원대국민포털(www.ecar.go.kr)에서 조회가 가능하므로 확인 바랍니다.</t>
   </si>
   <si>
     <t>경 기 도 자 동 차 매 매 사 업 조 합</t>
@@ -1232,46 +1225,46 @@
   <dimension ref="A1:AN47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.4" customWidth="true" style="0"/>
-    <col min="2" max="2" width="2.4" customWidth="true" style="0"/>
-    <col min="3" max="3" width="2.4" customWidth="true" style="0"/>
-    <col min="4" max="4" width="2.6" customWidth="true" style="0"/>
-    <col min="5" max="5" width="2.6" customWidth="true" style="0"/>
-    <col min="6" max="6" width="2.6" customWidth="true" style="0"/>
-    <col min="7" max="7" width="2.3" customWidth="true" style="0"/>
-    <col min="8" max="8" width="2.3" customWidth="true" style="0"/>
-    <col min="9" max="9" width="2.3" customWidth="true" style="0"/>
-    <col min="10" max="10" width="2.3" customWidth="true" style="0"/>
-    <col min="11" max="11" width="2.3" customWidth="true" style="0"/>
-    <col min="12" max="12" width="2.3" customWidth="true" style="0"/>
-    <col min="13" max="13" width="2.3" customWidth="true" style="0"/>
-    <col min="14" max="14" width="2.3" customWidth="true" style="0"/>
-    <col min="15" max="15" width="2.3" customWidth="true" style="0"/>
-    <col min="16" max="16" width="2.3" customWidth="true" style="0"/>
-    <col min="17" max="17" width="2.3" customWidth="true" style="0"/>
-    <col min="18" max="18" width="2.3" customWidth="true" style="0"/>
-    <col min="19" max="19" width="2.3" customWidth="true" style="0"/>
-    <col min="20" max="20" width="2.3" customWidth="true" style="0"/>
-    <col min="21" max="21" width="2.3" customWidth="true" style="0"/>
-    <col min="22" max="22" width="2.6" customWidth="true" style="0"/>
-    <col min="23" max="23" width="2.6" customWidth="true" style="0"/>
-    <col min="24" max="24" width="2.6" customWidth="true" style="0"/>
-    <col min="25" max="25" width="2.3" customWidth="true" style="0"/>
-    <col min="26" max="26" width="2.3" customWidth="true" style="0"/>
-    <col min="27" max="27" width="2.3" customWidth="true" style="0"/>
-    <col min="28" max="28" width="2.3" customWidth="true" style="0"/>
-    <col min="29" max="29" width="2.3" customWidth="true" style="0"/>
-    <col min="30" max="30" width="2.3" customWidth="true" style="0"/>
-    <col min="31" max="31" width="2.3" customWidth="true" style="0"/>
-    <col min="32" max="32" width="2.3" customWidth="true" style="0"/>
-    <col min="33" max="33" width="2.3" customWidth="true" style="0"/>
-    <col min="34" max="34" width="2.3" customWidth="true" style="0"/>
-    <col min="35" max="35" width="2.3" customWidth="true" style="0"/>
-    <col min="36" max="36" width="2.3" customWidth="true" style="0"/>
-    <col min="37" max="37" width="2.3" customWidth="true" style="0"/>
-    <col min="38" max="38" width="2.3" customWidth="true" style="0"/>
-    <col min="39" max="39" width="2.3" customWidth="true" style="0"/>
-    <col min="40" max="40" width="2.3" customWidth="true" style="0"/>
+    <col min="1" max="1" width="3.192" customWidth="true" style="0"/>
+    <col min="2" max="2" width="3.192" customWidth="true" style="0"/>
+    <col min="3" max="3" width="3.192" customWidth="true" style="0"/>
+    <col min="4" max="4" width="3.458" customWidth="true" style="0"/>
+    <col min="5" max="5" width="3.458" customWidth="true" style="0"/>
+    <col min="6" max="6" width="3.458" customWidth="true" style="0"/>
+    <col min="7" max="7" width="3.059" customWidth="true" style="0"/>
+    <col min="8" max="8" width="3.059" customWidth="true" style="0"/>
+    <col min="9" max="9" width="3.059" customWidth="true" style="0"/>
+    <col min="10" max="10" width="3.059" customWidth="true" style="0"/>
+    <col min="11" max="11" width="3.059" customWidth="true" style="0"/>
+    <col min="12" max="12" width="3.059" customWidth="true" style="0"/>
+    <col min="13" max="13" width="3.059" customWidth="true" style="0"/>
+    <col min="14" max="14" width="3.059" customWidth="true" style="0"/>
+    <col min="15" max="15" width="3.059" customWidth="true" style="0"/>
+    <col min="16" max="16" width="3.059" customWidth="true" style="0"/>
+    <col min="17" max="17" width="3.059" customWidth="true" style="0"/>
+    <col min="18" max="18" width="3.059" customWidth="true" style="0"/>
+    <col min="19" max="19" width="3.059" customWidth="true" style="0"/>
+    <col min="20" max="20" width="3.059" customWidth="true" style="0"/>
+    <col min="21" max="21" width="3.059" customWidth="true" style="0"/>
+    <col min="22" max="22" width="3.458" customWidth="true" style="0"/>
+    <col min="23" max="23" width="3.458" customWidth="true" style="0"/>
+    <col min="24" max="24" width="3.458" customWidth="true" style="0"/>
+    <col min="25" max="25" width="3.059" customWidth="true" style="0"/>
+    <col min="26" max="26" width="3.059" customWidth="true" style="0"/>
+    <col min="27" max="27" width="3.059" customWidth="true" style="0"/>
+    <col min="28" max="28" width="3.059" customWidth="true" style="0"/>
+    <col min="29" max="29" width="3.059" customWidth="true" style="0"/>
+    <col min="30" max="30" width="3.059" customWidth="true" style="0"/>
+    <col min="31" max="31" width="3.059" customWidth="true" style="0"/>
+    <col min="32" max="32" width="3.059" customWidth="true" style="0"/>
+    <col min="33" max="33" width="3.059" customWidth="true" style="0"/>
+    <col min="34" max="34" width="3.059" customWidth="true" style="0"/>
+    <col min="35" max="35" width="3.059" customWidth="true" style="0"/>
+    <col min="36" max="36" width="3.059" customWidth="true" style="0"/>
+    <col min="37" max="37" width="3.059" customWidth="true" style="0"/>
+    <col min="38" max="38" width="3.059" customWidth="true" style="0"/>
+    <col min="39" max="39" width="3.059" customWidth="true" style="0"/>
+    <col min="40" max="40" width="3.059" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" customHeight="1" ht="13">
@@ -2254,7 +2247,7 @@
       <c r="AM21" s="73"/>
       <c r="AN21" s="75"/>
     </row>
-    <row r="22" spans="1:40" customHeight="1" ht="46">
+    <row r="22" spans="1:40" customHeight="1" ht="36.8">
       <c r="A22" s="71" t="s">
         <v>46</v>
       </c>
@@ -2430,7 +2423,7 @@
       <c r="AM25" s="69"/>
       <c r="AN25" s="76"/>
     </row>
-    <row r="26" spans="1:40" customHeight="1" ht="55.2">
+    <row r="26" spans="1:40" customHeight="1" ht="36.8">
       <c r="A26" s="71" t="s">
         <v>50</v>
       </c>
@@ -2474,7 +2467,7 @@
       <c r="AM26" s="69"/>
       <c r="AN26" s="76"/>
     </row>
-    <row r="27" spans="1:40" customHeight="1" ht="27.6">
+    <row r="27" spans="1:40" customHeight="1" ht="18.4">
       <c r="A27" s="71" t="s">
         <v>51</v>
       </c>
@@ -3241,7 +3234,7 @@
       <c r="AM45" s="4"/>
       <c r="AN45" s="4"/>
     </row>
-    <row r="46" spans="1:40" customHeight="1" ht="55.2">
+    <row r="46" spans="1:40" customHeight="1" ht="36.8">
       <c r="A46" s="109" t="s">
         <v>74</v>
       </c>
@@ -3447,7 +3440,7 @@
     <mergeCell ref="AB47:AN47"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.28" right="0.28" top="0.28" bottom="0.2" header="0" footer="0"/>
+  <pageMargins left="0.28" right="0.28" top="0.24" bottom="0.16" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
   <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
     <oddHeader/>

--- a/resources/templates/system/transfer_certificate.xlsx
+++ b/resources/templates/system/transfer_certificate.xlsx
@@ -164,40 +164,37 @@
     <t>제1조 (당사자표시) 양도인을 "갑"이라 하고, 양수인을 "을"이라 한다.</t>
   </si>
   <si>
-    <t>제2조 (동시이행 등) ① "갑"은 잔금 수령과 상환으로 소유권이전등록에 필요한 서류와 매매목적물을 "을"에게 인도하기로 한다. 다만, "갑"과 "을"의 합의에 따라 매매금액의 2/3 이상의
-       상당액을 지급한 경우에는 매매목적물을 인도할 수 있다. ② "을"은 "갑"에게 잔금을 지급함과 동시에 소유권이전등록의 절차에 필요한 서류와 등록비용을 자동차매매업자(이하
-       "매매업자"라 한다)에게 내주어야 한다. 다만, 매매업자가 매수할 때에는 그러하지 아니하다. ③ 매매업자는 잔금지급일부터 15일 이내에 자동차소유권 이전등록 신청을 하여야
-       한다.</t>
-  </si>
-  <si>
-    <t>제3조 (공과금 부담) 이 자동차에 대한 제세공과금은 자동차 인도일을 기준으로 하여, 그 기준일까지의 분은 "갑"이 부담하고 기준일 다음날부터의 분은 "을"이 부담한다. 다만, 관계
-       법령에 제세공과금 납부에 관하여 특별한 규정이 있는 경우에는 그에 따른다.</t>
+    <t>제2조 (동시이행 등) ① "갑"은 잔금 수령과 상환으로 소유권이전등록에 필요한 서류와 매매목적물을 "을"에게 인도하기로 한다. 다만, "갑"과 "을"의 합의에 따라 매매금액의 2/3 이상의 상당액을 지급한
+       경우에는 매매목적물을 인도할 수 있다. ② "을"은 "갑"에게 잔금을 지급함과 동시에 소유권이전등록의 절차에 필요한 서류와 등록비용을 자동차매매업자(이하 "매매업자"라 한다)에게 내주어야 한다.
+       다만, 매매업자가 매수할 때에는 그러하지 아니하다. ③ 매매업자는 잔금지급일부터 15일 이내에 자동차소유권 이전등록 신청을 하여야 한다.</t>
+  </si>
+  <si>
+    <t>제3조 (공과금 부담) 이 자동차에 대한 제세공과금은 자동차 인도일을 기준으로 하여, 그 기준일까지의 분은 "갑"이 부담하고 기준일 다음날부터의 분은 "을"이 부담한다. 다만, 관계 법령에 제세공과금
+       납부에 관하여 특별한 규정이 있는 경우에는 그에 따른다.</t>
   </si>
   <si>
     <t>제4조 (사고책임) "을"은 이 자동차를 인수한 때부터 발생하는 모든 사고에 대하여 자기를 위하여 운행하는 자로서의 책임을 진다.</t>
   </si>
   <si>
-    <t>제5조 (법률상의 하자책임) ① 자동차 인도일 이전에 발생한 행정처분 또는 이전등록 요건의 불비 등의 하자에 대해서는 "갑"이 그 책임을 진다. ② 매매업자는 「자동차관리법」
-       제58조제1항에 따라 자동차의 성능 · 상태의 점검 내용을 "을"에게 알려야 하고, "을"이 원하는 경우 같은 법 제58조의4에 해당하는 자가 자동차 가격을 조사 · 산정한 내용을
-       알려야 한다.</t>
-  </si>
-  <si>
-    <t>제6조 (해약금 등) ① "갑"이 이 계약을 위반한 경우에는 "갑"은 해약금으로 계약금의 2배액을 "을"에게 배상해야 하며, "을"이 위약한 경우에는 "을"은 "갑"에게 계약금의 반환을 요구할
-       수 없다. 다만, 손해배상의 청구는 방해하지 않는다. ② 제5조제2항에 따라 "갑"이 고지한 자동차의 성능 · 상태의 점검내용 중 주행거리, 사고 또는 침수사실이 다르거나, "갑"이
-       자동차의 성능 · 상태의 점검내용 또는 압류 · 저당권의 등록 여부를 거짓으로 고지하거나 고지하지 아니한 경우 "을"은 자동차인도일로부터 30일 이내에 매매계약을 해제할 수
-       있으며, 이 경우 "을"은 자동차를 즉시 "갑"에게 반환하고 "갑"은 자동차의 반환과 동시에 이미 지급받은 매매금액을 "을"에게 반환하여야 한다.</t>
-  </si>
-  <si>
-    <t>제7조 (매매업자의 책임) 제5조의 하자에 대해서는 매매업자가 매도인과 동일한 책임을 지며, 시 · 도의 조례가 하자보증금을 예치하도록 하는 경우 매수인의 요청이 있을 때에는 그
-       하자보증금으로 매수인에게 우선 지급해야 한다. 다만, 매매업자는 양도인 또는 그 하자에 책임이 있는 자에 대하여 구상권을 행사할 수 있다.</t>
-  </si>
-  <si>
-    <t>제8조 (등록 지체 책임) "갑"과 "을"이 매매업자에게 이전등록의 대행에 필요한 서류 등의 발급 또는 권한의 위임을 한 후 매매업자가 이전등록 신청을 대행하지 않을 때에는 이에 대한
-       모든 책임은 매매업자가 진다.</t>
-  </si>
-  <si>
-    <t>제9조 (할부승계 특약) "갑"이 자동차를 할부로 구입하여 할부금을 다 내지 않은 상태에서 "을"에게 양도하는 경우에는 나머지 할부금을 "을"이 승계하여 부담할 것인지의 여부를
-       특약사항란에 적어야 한다.</t>
+    <t>제5조 (법률상의 하자책임) ① 자동차 인도일 이전에 발생한 행정처분 또는 이전등록 요건의 불비 등의 하자에 대해서는 "갑"이 그 책임을 진다. ② 매매업자는 「자동차관리법」 제58조제1항에 따라 자동차의
+       성능 · 상태의 점검 내용을 "을"에게 알려야 하고, "을"이 원하는 경우 같은 법 제58조의4에 해당하는 자가 자동차 가격을 조사 · 산정한 내용을 알려야 한다.</t>
+  </si>
+  <si>
+    <t>제6조 (해약금 등) ① "갑"이 이 계약을 위반한 경우에는 "갑"은 해약금으로 계약금의 2배액을 "을"에게 배상해야 하며, "을"이 위약한 경우에는 "을"은 "갑"에게 계약금의 반환을 요구할 수 없다. 다만,
+       손해배상의 청구는 방해하지 않는다. ② 제5조제2항에 따라 "갑"이 고지한 자동차의 성능 · 상태의 점검내용 중 주행거리, 사고 또는 침수사실이 다르거나, "갑"이 자동차의 성능 · 상태의 점검내용
+       또는 압류 · 저당권의 등록 여부를 거짓으로 고지하거나 고지하지 아니한 경우 "을"은 자동차인도일로부터 30일 이내에 매매계약을 해제할 수 있으며, 이 경우 "을"은 자동차를 즉시 "갑"에게
+       반환하고 "갑"은 자동차의 반환과 동시에 이미 지급받은 매매금액을 "을"에게 반환하여야 한다.</t>
+  </si>
+  <si>
+    <t>제7조 (매매업자의 책임) 제5조의 하자에 대해서는 매매업자가 매도인과 동일한 책임을 지며, 시 · 도의 조례가 하자보증금을 예치하도록 하는 경우 매수인의 요청이 있을 때에는 그 하자보증금으로
+       매수인에게 우선 지급해야 한다. 다만, 매매업자는 양도인 또는 그 하자에 책임이 있는 자에 대하여 구상권을 행사할 수 있다.</t>
+  </si>
+  <si>
+    <t>제8조 (등록 지체 책임) "갑"과 "을"이 매매업자에게 이전등록의 대행에 필요한 서류 등의 발급 또는 권한의 위임을 한 후 매매업자가 이전등록 신청을 대행하지 않을 때에는 이에 대한 모든 책임은
+       매매업자가 진다.</t>
+  </si>
+  <si>
+    <t>제9조 (할부승계 특약) "갑"이 자동차를 할부로 구입하여 할부금을 다 내지 않은 상태에서 "을"에게 양도하는 경우에는 나머지 할부금을 "을"이 승계하여 부담할 것인지의 여부를 특약사항란에 적어야 한다.</t>
   </si>
   <si>
     <t>제10조 (계약서) 이 계약서는 년 월 일 4통 작성하여 "갑"이 1통, "을"이 1통, 등록절차를 대행하는 매매업자가 2통씩을 각각 지닌다.</t>
@@ -264,10 +261,10 @@
     <t xml:space="preserve">  양수인</t>
   </si>
   <si>
-    <t>(유의사항) 1. 이 양도증명서는 「자동차관리법」에 따라 자동차매매업의 등록을 한 자만이 사용할 수 있습니다. 2. 매매업자는 반드시 직인을 찍어야 합니다. 3. 자동차매매사업조합의
-              중고자동차 제시 또는 매도신고번호를 적어야 합니다. 4. 이 양도증명서를 작성할 때 매매대상 중고자동차의 배출가스저감장치 자기부담금의 납부 여부를 확인하여 뜻하지
-              않은 손해를 입지 않도록 하시기 바랍니다. 5. 자동차정비, 검사, 주행거리 이력, 자동차세 납부 여부, 압류내역 및 배출가스저감장치 자기부담금 납부내역 등
-              자동차토탈이력정보는 국토교통부에서 제공하는 스마트폰용 어플("마이카정보") 또는 자동차민원대국민포털(www.ecar.go.kr)에서 조회가 가능하므로 확인 바랍니다.</t>
+    <t>(유의사항) 1. 이 양도증명서는 「자동차관리법」에 따라 자동차매매업의 등록을 한 자만이 사용할 수 있습니다. 2. 매매업자는 반드시 직인을 찍어야 합니다. 3. 자동차매매사업조합의 중고자동차 제시 또는
+              매도신고번호를 적어야 합니다. 4. 이 양도증명서를 작성할 때 매매대상 중고자동차의 배출가스저감장치 자기부담금의 납부 여부를 확인하여 뜻하지 않은 손해를 입지 않도록 하시기 바랍니다.
+              5. 자동차정비, 검사, 주행거리 이력, 자동차세 납부 여부, 압류내역 및 배출가스저감장치 자기부담금 납부내역 등 자동차토탈이력정보는 국토교통부에서 제공하는 스마트폰용
+              어플("마이카정보") 또는 자동차민원대국민포털(www.ecar.go.kr)에서 조회가 가능하므로 확인 바랍니다.</t>
   </si>
   <si>
     <t>경 기 도 자 동 차 매 매 사 업 조 합</t>
@@ -1225,46 +1222,46 @@
   <dimension ref="A1:AN47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="3.192" customWidth="true" style="0"/>
-    <col min="2" max="2" width="3.192" customWidth="true" style="0"/>
-    <col min="3" max="3" width="3.192" customWidth="true" style="0"/>
-    <col min="4" max="4" width="3.458" customWidth="true" style="0"/>
-    <col min="5" max="5" width="3.458" customWidth="true" style="0"/>
-    <col min="6" max="6" width="3.458" customWidth="true" style="0"/>
-    <col min="7" max="7" width="3.059" customWidth="true" style="0"/>
-    <col min="8" max="8" width="3.059" customWidth="true" style="0"/>
-    <col min="9" max="9" width="3.059" customWidth="true" style="0"/>
-    <col min="10" max="10" width="3.059" customWidth="true" style="0"/>
-    <col min="11" max="11" width="3.059" customWidth="true" style="0"/>
-    <col min="12" max="12" width="3.059" customWidth="true" style="0"/>
-    <col min="13" max="13" width="3.059" customWidth="true" style="0"/>
-    <col min="14" max="14" width="3.059" customWidth="true" style="0"/>
-    <col min="15" max="15" width="3.059" customWidth="true" style="0"/>
-    <col min="16" max="16" width="3.059" customWidth="true" style="0"/>
-    <col min="17" max="17" width="3.059" customWidth="true" style="0"/>
-    <col min="18" max="18" width="3.059" customWidth="true" style="0"/>
-    <col min="19" max="19" width="3.059" customWidth="true" style="0"/>
-    <col min="20" max="20" width="3.059" customWidth="true" style="0"/>
-    <col min="21" max="21" width="3.059" customWidth="true" style="0"/>
-    <col min="22" max="22" width="3.458" customWidth="true" style="0"/>
-    <col min="23" max="23" width="3.458" customWidth="true" style="0"/>
-    <col min="24" max="24" width="3.458" customWidth="true" style="0"/>
-    <col min="25" max="25" width="3.059" customWidth="true" style="0"/>
-    <col min="26" max="26" width="3.059" customWidth="true" style="0"/>
-    <col min="27" max="27" width="3.059" customWidth="true" style="0"/>
-    <col min="28" max="28" width="3.059" customWidth="true" style="0"/>
-    <col min="29" max="29" width="3.059" customWidth="true" style="0"/>
-    <col min="30" max="30" width="3.059" customWidth="true" style="0"/>
-    <col min="31" max="31" width="3.059" customWidth="true" style="0"/>
-    <col min="32" max="32" width="3.059" customWidth="true" style="0"/>
-    <col min="33" max="33" width="3.059" customWidth="true" style="0"/>
-    <col min="34" max="34" width="3.059" customWidth="true" style="0"/>
-    <col min="35" max="35" width="3.059" customWidth="true" style="0"/>
-    <col min="36" max="36" width="3.059" customWidth="true" style="0"/>
-    <col min="37" max="37" width="3.059" customWidth="true" style="0"/>
-    <col min="38" max="38" width="3.059" customWidth="true" style="0"/>
-    <col min="39" max="39" width="3.059" customWidth="true" style="0"/>
-    <col min="40" max="40" width="3.059" customWidth="true" style="0"/>
+    <col min="1" max="1" width="3.528" customWidth="true" style="0"/>
+    <col min="2" max="2" width="3.528" customWidth="true" style="0"/>
+    <col min="3" max="3" width="3.528" customWidth="true" style="0"/>
+    <col min="4" max="4" width="3.822" customWidth="true" style="0"/>
+    <col min="5" max="5" width="3.822" customWidth="true" style="0"/>
+    <col min="6" max="6" width="3.822" customWidth="true" style="0"/>
+    <col min="7" max="7" width="3.381" customWidth="true" style="0"/>
+    <col min="8" max="8" width="3.381" customWidth="true" style="0"/>
+    <col min="9" max="9" width="3.381" customWidth="true" style="0"/>
+    <col min="10" max="10" width="3.381" customWidth="true" style="0"/>
+    <col min="11" max="11" width="3.381" customWidth="true" style="0"/>
+    <col min="12" max="12" width="3.381" customWidth="true" style="0"/>
+    <col min="13" max="13" width="3.381" customWidth="true" style="0"/>
+    <col min="14" max="14" width="3.381" customWidth="true" style="0"/>
+    <col min="15" max="15" width="3.381" customWidth="true" style="0"/>
+    <col min="16" max="16" width="3.381" customWidth="true" style="0"/>
+    <col min="17" max="17" width="3.381" customWidth="true" style="0"/>
+    <col min="18" max="18" width="3.381" customWidth="true" style="0"/>
+    <col min="19" max="19" width="3.381" customWidth="true" style="0"/>
+    <col min="20" max="20" width="3.381" customWidth="true" style="0"/>
+    <col min="21" max="21" width="3.381" customWidth="true" style="0"/>
+    <col min="22" max="22" width="3.822" customWidth="true" style="0"/>
+    <col min="23" max="23" width="3.822" customWidth="true" style="0"/>
+    <col min="24" max="24" width="3.822" customWidth="true" style="0"/>
+    <col min="25" max="25" width="3.381" customWidth="true" style="0"/>
+    <col min="26" max="26" width="3.381" customWidth="true" style="0"/>
+    <col min="27" max="27" width="3.381" customWidth="true" style="0"/>
+    <col min="28" max="28" width="3.381" customWidth="true" style="0"/>
+    <col min="29" max="29" width="3.381" customWidth="true" style="0"/>
+    <col min="30" max="30" width="3.381" customWidth="true" style="0"/>
+    <col min="31" max="31" width="3.381" customWidth="true" style="0"/>
+    <col min="32" max="32" width="3.381" customWidth="true" style="0"/>
+    <col min="33" max="33" width="3.381" customWidth="true" style="0"/>
+    <col min="34" max="34" width="3.381" customWidth="true" style="0"/>
+    <col min="35" max="35" width="3.381" customWidth="true" style="0"/>
+    <col min="36" max="36" width="3.381" customWidth="true" style="0"/>
+    <col min="37" max="37" width="3.381" customWidth="true" style="0"/>
+    <col min="38" max="38" width="3.381" customWidth="true" style="0"/>
+    <col min="39" max="39" width="3.381" customWidth="true" style="0"/>
+    <col min="40" max="40" width="3.381" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" customHeight="1" ht="13">
@@ -2247,7 +2244,7 @@
       <c r="AM21" s="73"/>
       <c r="AN21" s="75"/>
     </row>
-    <row r="22" spans="1:40" customHeight="1" ht="36.8">
+    <row r="22" spans="1:40" customHeight="1" ht="27.6">
       <c r="A22" s="71" t="s">
         <v>46</v>
       </c>
@@ -2379,7 +2376,7 @@
       <c r="AM24" s="69"/>
       <c r="AN24" s="76"/>
     </row>
-    <row r="25" spans="1:40" customHeight="1" ht="27.6">
+    <row r="25" spans="1:40" customHeight="1" ht="18.4">
       <c r="A25" s="71" t="s">
         <v>49</v>
       </c>
@@ -2555,7 +2552,7 @@
       <c r="AM28" s="69"/>
       <c r="AN28" s="76"/>
     </row>
-    <row r="29" spans="1:40" customHeight="1" ht="18.4">
+    <row r="29" spans="1:40" customHeight="1" ht="9.2">
       <c r="A29" s="71" t="s">
         <v>53</v>
       </c>
@@ -3279,22 +3276,22 @@
       <c r="AN46" s="111"/>
     </row>
     <row r="47" spans="1:40" customHeight="1" ht="18">
-      <c r="A47" s="112" t="s">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="112" t="s">
         <v>75</v>
       </c>
-      <c r="B47" s="112"/>
-      <c r="C47" s="112"/>
-      <c r="D47" s="112"/>
-      <c r="E47" s="112"/>
-      <c r="F47" s="112"/>
-      <c r="G47" s="112"/>
-      <c r="H47" s="112"/>
-      <c r="I47" s="112"/>
-      <c r="J47" s="112"/>
-      <c r="K47" s="112"/>
-      <c r="L47" s="112"/>
-      <c r="M47" s="112"/>
-      <c r="N47" s="112"/>
       <c r="O47" s="112"/>
       <c r="P47" s="112"/>
       <c r="Q47" s="112"/>
@@ -3436,7 +3433,8 @@
     <mergeCell ref="AC45:AH45"/>
     <mergeCell ref="AI45:AN45"/>
     <mergeCell ref="A46:AN46"/>
-    <mergeCell ref="A47:AA47"/>
+    <mergeCell ref="A47:M47"/>
+    <mergeCell ref="N47:AA47"/>
     <mergeCell ref="AB47:AN47"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>

--- a/resources/templates/system/transfer_certificate.xlsx
+++ b/resources/templates/system/transfer_certificate.xlsx
@@ -1625,8 +1625,8 @@
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
       <c r="L5" s="124"/>
       <c r="M5" s="124"/>
       <c r="N5" s="124"/>
@@ -1649,11 +1649,11 @@
       </c>
       <c r="Z5" s="12"/>
       <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="24" t="s">
+      <c r="AB5" s="24" t="s">
         <v>14</v>
       </c>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="24"/>
       <c r="AE5" s="24"/>
       <c r="AF5" s="24"/>
       <c r="AG5" s="24"/>
@@ -1679,8 +1679,8 @@
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
       <c r="L6" s="24"/>
       <c r="M6" s="24"/>
       <c r="N6" s="24"/>
@@ -1699,11 +1699,11 @@
       </c>
       <c r="Z6" s="12"/>
       <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="24" t="s">
+      <c r="AB6" s="24" t="s">
         <v>15</v>
       </c>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
       <c r="AE6" s="24"/>
       <c r="AF6" s="24"/>
       <c r="AG6" s="24"/>
@@ -1727,8 +1727,8 @@
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
       <c r="L7" s="125"/>
       <c r="M7" s="125"/>
       <c r="N7" s="125"/>
@@ -1747,11 +1747,11 @@
       </c>
       <c r="Z7" s="12"/>
       <c r="AA7" s="12"/>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="28" t="s">
+      <c r="AB7" s="28" t="s">
         <v>16</v>
       </c>
+      <c r="AC7" s="28"/>
+      <c r="AD7" s="28"/>
       <c r="AE7" s="28"/>
       <c r="AF7" s="28"/>
       <c r="AG7" s="28"/>
@@ -2377,7 +2377,7 @@
       <c r="AM20" s="24"/>
       <c r="AN20" s="111"/>
     </row>
-    <row r="21" spans="1:40" customHeight="1" ht="9.2">
+    <row r="21" spans="1:40" customHeight="1" ht="15">
       <c r="A21" s="101" t="s">
         <v>45</v>
       </c>
@@ -2421,7 +2421,7 @@
       <c r="AM21" s="58"/>
       <c r="AN21" s="118"/>
     </row>
-    <row r="22" spans="1:40" customHeight="1" ht="27.6">
+    <row r="22" spans="1:40" customHeight="1" ht="33.6">
       <c r="A22" s="101" t="s">
         <v>46</v>
       </c>
@@ -2465,7 +2465,7 @@
       <c r="AM22" s="58"/>
       <c r="AN22" s="118"/>
     </row>
-    <row r="23" spans="1:40" customHeight="1" ht="18.4">
+    <row r="23" spans="1:40" customHeight="1" ht="24.6">
       <c r="A23" s="101" t="s">
         <v>47</v>
       </c>
@@ -2641,7 +2641,7 @@
       <c r="AM26" s="58"/>
       <c r="AN26" s="118"/>
     </row>
-    <row r="27" spans="1:40" customHeight="1" ht="18.4">
+    <row r="27" spans="1:40" customHeight="1" ht="22.8">
       <c r="A27" s="101" t="s">
         <v>51</v>
       </c>
@@ -2685,7 +2685,7 @@
       <c r="AM27" s="58"/>
       <c r="AN27" s="118"/>
     </row>
-    <row r="28" spans="1:40" customHeight="1" ht="18.4">
+    <row r="28" spans="1:40" customHeight="1" ht="21">
       <c r="A28" s="101" t="s">
         <v>52</v>
       </c>
@@ -2729,7 +2729,7 @@
       <c r="AM28" s="58"/>
       <c r="AN28" s="118"/>
     </row>
-    <row r="29" spans="1:40" customHeight="1" ht="9.2">
+    <row r="29" spans="1:40" customHeight="1" ht="12">
       <c r="A29" s="101" t="s">
         <v>53</v>
       </c>
@@ -2773,7 +2773,7 @@
       <c r="AM29" s="58"/>
       <c r="AN29" s="118"/>
     </row>
-    <row r="30" spans="1:40" customHeight="1" ht="9.2">
+    <row r="30" spans="1:40" customHeight="1" ht="14.4">
       <c r="A30" s="101" t="s">
         <v>54</v>
       </c>
@@ -3596,20 +3596,20 @@
     <mergeCell ref="A5:C7"/>
     <mergeCell ref="D5:F7"/>
     <mergeCell ref="V5:X7"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="L5:P5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:P5"/>
     <mergeCell ref="Q5:U5"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="L6:U6"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="L7:U7"/>
-    <mergeCell ref="Y5:AC5"/>
-    <mergeCell ref="AD5:AH5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:U6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:U7"/>
+    <mergeCell ref="Y5:AA5"/>
+    <mergeCell ref="AB5:AH5"/>
     <mergeCell ref="AI5:AN5"/>
-    <mergeCell ref="Y6:AC6"/>
-    <mergeCell ref="AD6:AN6"/>
-    <mergeCell ref="Y7:AC7"/>
-    <mergeCell ref="AD7:AN7"/>
+    <mergeCell ref="Y6:AA6"/>
+    <mergeCell ref="AB6:AN6"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="AB7:AN7"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="H8:W8"/>
@@ -3700,7 +3700,7 @@
     <mergeCell ref="AB47:AN47"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.28" right="0.28" top="0.24" bottom="0.16" header="0" footer="0"/>
+  <pageMargins left="0.28" right="0.28" top="0.39" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
   <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
     <oddHeader/>

--- a/resources/templates/system/transfer_certificate.xlsx
+++ b/resources/templates/system/transfer_certificate.xlsx
@@ -672,7 +672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="145">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
@@ -716,6 +716,9 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
+    </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
     </xf>
@@ -1095,6 +1098,9 @@
     </xf>
     <xf xfId="0" fontId="9" numFmtId="164" fillId="2" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1474,51 +1480,51 @@
       <c r="AN1" s="2"/>
     </row>
     <row r="2" spans="1:40" customHeight="1" ht="22">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105"/>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="105"/>
-      <c r="U2" s="105"/>
-      <c r="V2" s="105"/>
-      <c r="W2" s="105"/>
-      <c r="X2" s="105"/>
-      <c r="Y2" s="105"/>
-      <c r="Z2" s="105"/>
-      <c r="AA2" s="105"/>
-      <c r="AB2" s="105"/>
-      <c r="AC2" s="105"/>
-      <c r="AD2" s="105"/>
-      <c r="AE2" s="105"/>
-      <c r="AF2" s="105"/>
-      <c r="AG2" s="105"/>
-      <c r="AH2" s="105"/>
-      <c r="AI2" s="105"/>
-      <c r="AJ2" s="105"/>
-      <c r="AK2" s="105"/>
-      <c r="AL2" s="105"/>
-      <c r="AM2" s="105"/>
-      <c r="AN2" s="107"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="106"/>
+      <c r="AA2" s="106"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="106"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="106"/>
+      <c r="AH2" s="106"/>
+      <c r="AI2" s="106"/>
+      <c r="AJ2" s="106"/>
+      <c r="AK2" s="106"/>
+      <c r="AL2" s="106"/>
+      <c r="AM2" s="106"/>
+      <c r="AN2" s="108"/>
     </row>
     <row r="3" spans="1:40" customHeight="1" ht="16">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="5"/>
@@ -1563,10 +1569,10 @@
       <c r="AK3" s="7"/>
       <c r="AL3" s="7"/>
       <c r="AM3" s="7"/>
-      <c r="AN3" s="108"/>
+      <c r="AN3" s="109"/>
     </row>
     <row r="4" spans="1:40" customHeight="1" ht="16">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="94" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="9"/>
@@ -1607,242 +1613,242 @@
       <c r="AK4" s="12"/>
       <c r="AL4" s="12"/>
       <c r="AM4" s="12"/>
-      <c r="AN4" s="109"/>
+      <c r="AN4" s="110"/>
     </row>
     <row r="5" spans="1:40" customHeight="1" ht="17">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="16" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="21"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="22"/>
       <c r="G5" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="124"/>
-      <c r="P5" s="124"/>
-      <c r="Q5" s="25" t="s">
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="16" t="s">
+      <c r="R5" s="26"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="19"/>
-      <c r="X5" s="21"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="22"/>
       <c r="Y5" s="11" t="s">
         <v>10</v>
       </c>
       <c r="Z5" s="12"/>
       <c r="AA5" s="12"/>
-      <c r="AB5" s="24" t="s">
+      <c r="AB5" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AC5" s="24"/>
-      <c r="AD5" s="24"/>
-      <c r="AE5" s="24"/>
-      <c r="AF5" s="24"/>
-      <c r="AG5" s="24"/>
-      <c r="AH5" s="24"/>
-      <c r="AI5" s="25" t="s">
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="25"/>
+      <c r="AG5" s="25"/>
+      <c r="AH5" s="25"/>
+      <c r="AI5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="AJ5" s="25"/>
-      <c r="AK5" s="25"/>
-      <c r="AL5" s="25"/>
-      <c r="AM5" s="25"/>
-      <c r="AN5" s="110"/>
+      <c r="AJ5" s="26"/>
+      <c r="AK5" s="26"/>
+      <c r="AL5" s="26"/>
+      <c r="AM5" s="26"/>
+      <c r="AN5" s="111"/>
     </row>
     <row r="6" spans="1:40" customHeight="1" ht="17">
-      <c r="A6" s="95"/>
+      <c r="A6" s="96"/>
       <c r="B6" s="14"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="14"/>
-      <c r="F6" s="22"/>
+      <c r="F6" s="23"/>
       <c r="G6" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="17"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="18"/>
       <c r="W6" s="14"/>
-      <c r="X6" s="22"/>
+      <c r="X6" s="23"/>
       <c r="Y6" s="11" t="s">
         <v>12</v>
       </c>
       <c r="Z6" s="12"/>
       <c r="AA6" s="12"/>
-      <c r="AB6" s="24" t="s">
+      <c r="AB6" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="24"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="24"/>
-      <c r="AH6" s="24"/>
-      <c r="AI6" s="24"/>
-      <c r="AJ6" s="24"/>
-      <c r="AK6" s="24"/>
-      <c r="AL6" s="24"/>
-      <c r="AM6" s="24"/>
-      <c r="AN6" s="111"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="25"/>
+      <c r="AK6" s="25"/>
+      <c r="AL6" s="25"/>
+      <c r="AM6" s="25"/>
+      <c r="AN6" s="112"/>
     </row>
     <row r="7" spans="1:40" customHeight="1" ht="17">
-      <c r="A7" s="96"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="23"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="24"/>
       <c r="G7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="125"/>
-      <c r="L7" s="125"/>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="125"/>
-      <c r="R7" s="125"/>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="126"/>
-      <c r="V7" s="18"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="23"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="126"/>
+      <c r="M7" s="126"/>
+      <c r="N7" s="126"/>
+      <c r="O7" s="126"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="126"/>
+      <c r="U7" s="127"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="24"/>
       <c r="Y7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="Z7" s="12"/>
       <c r="AA7" s="12"/>
-      <c r="AB7" s="28" t="s">
+      <c r="AB7" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="28"/>
-      <c r="AH7" s="28"/>
-      <c r="AI7" s="28"/>
-      <c r="AJ7" s="28"/>
-      <c r="AK7" s="28"/>
-      <c r="AL7" s="28"/>
-      <c r="AM7" s="28"/>
-      <c r="AN7" s="112"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="113"/>
     </row>
     <row r="8" spans="1:40" customHeight="1" ht="17">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="21"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="13"/>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="31"/>
-      <c r="X8" s="29" t="s">
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="30"/>
-      <c r="AD8" s="30"/>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="30"/>
-      <c r="AH8" s="30"/>
-      <c r="AI8" s="30"/>
-      <c r="AJ8" s="30"/>
-      <c r="AK8" s="30"/>
-      <c r="AL8" s="30"/>
-      <c r="AM8" s="30"/>
-      <c r="AN8" s="113"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="31"/>
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="31"/>
+      <c r="AK8" s="31"/>
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="114"/>
     </row>
     <row r="9" spans="1:40" customHeight="1" ht="17">
-      <c r="A9" s="95"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="14"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="32" t="s">
+      <c r="C9" s="23"/>
+      <c r="D9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="29" t="s">
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="25" t="s">
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="27"/>
       <c r="X9" s="11"/>
       <c r="Y9" s="12"/>
       <c r="Z9" s="12"/>
@@ -1856,43 +1862,43 @@
       <c r="AH9" s="12"/>
       <c r="AI9" s="12"/>
       <c r="AJ9" s="12"/>
-      <c r="AK9" s="25" t="s">
+      <c r="AK9" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="AL9" s="25"/>
-      <c r="AM9" s="25"/>
-      <c r="AN9" s="110"/>
+      <c r="AL9" s="26"/>
+      <c r="AM9" s="26"/>
+      <c r="AN9" s="111"/>
     </row>
     <row r="10" spans="1:40" customHeight="1" ht="17">
-      <c r="A10" s="96"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="32" t="s">
+      <c r="A10" s="97"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="29" t="s">
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="25" t="s">
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="27"/>
       <c r="X10" s="11"/>
       <c r="Y10" s="12"/>
       <c r="Z10" s="12"/>
@@ -1906,23 +1912,23 @@
       <c r="AH10" s="12"/>
       <c r="AI10" s="12"/>
       <c r="AJ10" s="12"/>
-      <c r="AK10" s="25" t="s">
+      <c r="AK10" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="AL10" s="25"/>
-      <c r="AM10" s="25"/>
-      <c r="AN10" s="110"/>
+      <c r="AL10" s="26"/>
+      <c r="AM10" s="26"/>
+      <c r="AN10" s="111"/>
     </row>
     <row r="11" spans="1:40" customHeight="1" ht="17">
-      <c r="A11" s="97" t="s">
+      <c r="A11" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="37"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="8" t="s">
         <v>27</v>
       </c>
@@ -1957,984 +1963,984 @@
       <c r="AK11" s="9"/>
       <c r="AL11" s="9"/>
       <c r="AM11" s="9"/>
-      <c r="AN11" s="114"/>
+      <c r="AN11" s="115"/>
     </row>
     <row r="12" spans="1:40" customHeight="1" ht="19">
-      <c r="A12" s="98" t="s">
+      <c r="A12" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="115"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="39"/>
+      <c r="V12" s="39"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="39"/>
+      <c r="Y12" s="39"/>
+      <c r="Z12" s="39"/>
+      <c r="AA12" s="39"/>
+      <c r="AB12" s="39"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39"/>
+      <c r="AF12" s="39"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="39"/>
+      <c r="AI12" s="39"/>
+      <c r="AJ12" s="39"/>
+      <c r="AK12" s="39"/>
+      <c r="AL12" s="39"/>
+      <c r="AM12" s="39"/>
+      <c r="AN12" s="116"/>
     </row>
     <row r="13" spans="1:40" customHeight="1" ht="17">
-      <c r="A13" s="97" t="s">
+      <c r="A13" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="124"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="124"/>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="124"/>
-      <c r="S13" s="128"/>
-      <c r="T13" s="35" t="s">
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="125"/>
+      <c r="K13" s="125"/>
+      <c r="L13" s="125"/>
+      <c r="M13" s="125"/>
+      <c r="N13" s="125"/>
+      <c r="O13" s="125"/>
+      <c r="P13" s="125"/>
+      <c r="Q13" s="125"/>
+      <c r="R13" s="125"/>
+      <c r="S13" s="129"/>
+      <c r="T13" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="U13" s="36"/>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="129"/>
-      <c r="Z13" s="130"/>
-      <c r="AA13" s="130"/>
-      <c r="AB13" s="130"/>
-      <c r="AC13" s="130"/>
-      <c r="AD13" s="130"/>
-      <c r="AE13" s="130"/>
-      <c r="AF13" s="130"/>
-      <c r="AG13" s="130"/>
-      <c r="AH13" s="130"/>
-      <c r="AI13" s="130"/>
-      <c r="AJ13" s="130"/>
-      <c r="AK13" s="130"/>
-      <c r="AL13" s="130"/>
-      <c r="AM13" s="130"/>
-      <c r="AN13" s="131"/>
+      <c r="U13" s="37"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="37"/>
+      <c r="X13" s="38"/>
+      <c r="Y13" s="130"/>
+      <c r="Z13" s="131"/>
+      <c r="AA13" s="131"/>
+      <c r="AB13" s="131"/>
+      <c r="AC13" s="131"/>
+      <c r="AD13" s="131"/>
+      <c r="AE13" s="131"/>
+      <c r="AF13" s="131"/>
+      <c r="AG13" s="131"/>
+      <c r="AH13" s="131"/>
+      <c r="AI13" s="131"/>
+      <c r="AJ13" s="131"/>
+      <c r="AK13" s="131"/>
+      <c r="AL13" s="131"/>
+      <c r="AM13" s="131"/>
+      <c r="AN13" s="132"/>
     </row>
     <row r="14" spans="1:40" customHeight="1" ht="17">
-      <c r="A14" s="97" t="s">
+      <c r="A14" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="124"/>
-      <c r="K14" s="124"/>
-      <c r="L14" s="124"/>
-      <c r="M14" s="124"/>
-      <c r="N14" s="124"/>
-      <c r="O14" s="124"/>
-      <c r="P14" s="124"/>
-      <c r="Q14" s="124"/>
-      <c r="R14" s="124"/>
-      <c r="S14" s="128"/>
-      <c r="T14" s="35" t="s">
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="125"/>
+      <c r="K14" s="125"/>
+      <c r="L14" s="125"/>
+      <c r="M14" s="125"/>
+      <c r="N14" s="125"/>
+      <c r="O14" s="125"/>
+      <c r="P14" s="125"/>
+      <c r="Q14" s="125"/>
+      <c r="R14" s="125"/>
+      <c r="S14" s="129"/>
+      <c r="T14" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="U14" s="36"/>
-      <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="37"/>
-      <c r="Y14" s="127"/>
-      <c r="Z14" s="124"/>
-      <c r="AA14" s="124"/>
-      <c r="AB14" s="124"/>
-      <c r="AC14" s="124"/>
-      <c r="AD14" s="124"/>
-      <c r="AE14" s="124"/>
-      <c r="AF14" s="124"/>
-      <c r="AG14" s="124"/>
-      <c r="AH14" s="124"/>
-      <c r="AI14" s="124"/>
-      <c r="AJ14" s="124"/>
-      <c r="AK14" s="124"/>
-      <c r="AL14" s="124"/>
-      <c r="AM14" s="124"/>
-      <c r="AN14" s="132"/>
+      <c r="U14" s="37"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="128"/>
+      <c r="Z14" s="125"/>
+      <c r="AA14" s="125"/>
+      <c r="AB14" s="125"/>
+      <c r="AC14" s="125"/>
+      <c r="AD14" s="125"/>
+      <c r="AE14" s="125"/>
+      <c r="AF14" s="125"/>
+      <c r="AG14" s="125"/>
+      <c r="AH14" s="125"/>
+      <c r="AI14" s="125"/>
+      <c r="AJ14" s="125"/>
+      <c r="AK14" s="125"/>
+      <c r="AL14" s="125"/>
+      <c r="AM14" s="125"/>
+      <c r="AN14" s="133"/>
     </row>
     <row r="15" spans="1:40" customHeight="1" ht="17">
-      <c r="A15" s="97" t="s">
+      <c r="A15" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="124"/>
-      <c r="J15" s="124"/>
-      <c r="K15" s="124"/>
-      <c r="L15" s="124"/>
-      <c r="M15" s="124"/>
-      <c r="N15" s="124"/>
-      <c r="O15" s="124"/>
-      <c r="P15" s="124"/>
-      <c r="Q15" s="124"/>
-      <c r="R15" s="124"/>
-      <c r="S15" s="128"/>
-      <c r="T15" s="35" t="s">
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="129"/>
+      <c r="T15" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="U15" s="36"/>
-      <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="37"/>
-      <c r="Y15" s="133"/>
-      <c r="Z15" s="134"/>
-      <c r="AA15" s="134"/>
-      <c r="AB15" s="134"/>
-      <c r="AC15" s="134"/>
-      <c r="AD15" s="134"/>
-      <c r="AE15" s="135"/>
-      <c r="AF15" s="135"/>
-      <c r="AG15" s="135"/>
-      <c r="AH15" s="135"/>
-      <c r="AI15" s="135"/>
-      <c r="AJ15" s="135"/>
-      <c r="AK15" s="135"/>
-      <c r="AL15" s="135"/>
-      <c r="AM15" s="135"/>
-      <c r="AN15" s="136"/>
+      <c r="U15" s="37"/>
+      <c r="V15" s="37"/>
+      <c r="W15" s="37"/>
+      <c r="X15" s="38"/>
+      <c r="Y15" s="134"/>
+      <c r="Z15" s="135"/>
+      <c r="AA15" s="135"/>
+      <c r="AB15" s="135"/>
+      <c r="AC15" s="135"/>
+      <c r="AD15" s="135"/>
+      <c r="AE15" s="136"/>
+      <c r="AF15" s="136"/>
+      <c r="AG15" s="136"/>
+      <c r="AH15" s="136"/>
+      <c r="AI15" s="136"/>
+      <c r="AJ15" s="136"/>
+      <c r="AK15" s="136"/>
+      <c r="AL15" s="136"/>
+      <c r="AM15" s="136"/>
+      <c r="AN15" s="137"/>
     </row>
     <row r="16" spans="1:40" customHeight="1" ht="17">
-      <c r="A16" s="97" t="s">
+      <c r="A16" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="40">
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="41">
         <v>0</v>
       </c>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="40"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="35" t="s">
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="U16" s="36"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="133"/>
-      <c r="Z16" s="134"/>
-      <c r="AA16" s="134"/>
-      <c r="AB16" s="134"/>
-      <c r="AC16" s="134"/>
-      <c r="AD16" s="134"/>
-      <c r="AE16" s="135"/>
-      <c r="AF16" s="135"/>
-      <c r="AG16" s="135"/>
-      <c r="AH16" s="135"/>
-      <c r="AI16" s="135"/>
-      <c r="AJ16" s="135"/>
-      <c r="AK16" s="135"/>
-      <c r="AL16" s="135"/>
-      <c r="AM16" s="135"/>
-      <c r="AN16" s="136"/>
+      <c r="U16" s="37"/>
+      <c r="V16" s="37"/>
+      <c r="W16" s="37"/>
+      <c r="X16" s="38"/>
+      <c r="Y16" s="134"/>
+      <c r="Z16" s="135"/>
+      <c r="AA16" s="135"/>
+      <c r="AB16" s="135"/>
+      <c r="AC16" s="135"/>
+      <c r="AD16" s="135"/>
+      <c r="AE16" s="136"/>
+      <c r="AF16" s="136"/>
+      <c r="AG16" s="136"/>
+      <c r="AH16" s="136"/>
+      <c r="AI16" s="136"/>
+      <c r="AJ16" s="136"/>
+      <c r="AK16" s="136"/>
+      <c r="AL16" s="136"/>
+      <c r="AM16" s="136"/>
+      <c r="AN16" s="137"/>
     </row>
     <row r="17" spans="1:40" customHeight="1" ht="17">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="139"/>
-      <c r="H17" s="139"/>
-      <c r="I17" s="139"/>
-      <c r="J17" s="139"/>
-      <c r="K17" s="139"/>
-      <c r="L17" s="139"/>
-      <c r="M17" s="139"/>
-      <c r="N17" s="139"/>
-      <c r="O17" s="139"/>
-      <c r="P17" s="139"/>
-      <c r="Q17" s="139"/>
-      <c r="R17" s="139"/>
-      <c r="S17" s="141"/>
-      <c r="T17" s="46" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="140"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="140"/>
+      <c r="K17" s="140"/>
+      <c r="L17" s="140"/>
+      <c r="M17" s="140"/>
+      <c r="N17" s="140"/>
+      <c r="O17" s="140"/>
+      <c r="P17" s="140"/>
+      <c r="Q17" s="140"/>
+      <c r="R17" s="140"/>
+      <c r="S17" s="142"/>
+      <c r="T17" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="U17" s="48"/>
-      <c r="V17" s="48"/>
-      <c r="W17" s="48"/>
-      <c r="X17" s="50"/>
-      <c r="Y17" s="52" t="s">
+      <c r="U17" s="49"/>
+      <c r="V17" s="49"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="51"/>
+      <c r="Y17" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Z17" s="53"/>
-      <c r="AA17" s="53"/>
-      <c r="AB17" s="53"/>
-      <c r="AC17" s="53"/>
-      <c r="AD17" s="53"/>
-      <c r="AE17" s="53"/>
-      <c r="AF17" s="53"/>
-      <c r="AG17" s="53"/>
-      <c r="AH17" s="53"/>
-      <c r="AI17" s="53"/>
-      <c r="AJ17" s="53"/>
-      <c r="AK17" s="53"/>
-      <c r="AL17" s="53"/>
-      <c r="AM17" s="53"/>
-      <c r="AN17" s="117"/>
+      <c r="Z17" s="54"/>
+      <c r="AA17" s="54"/>
+      <c r="AB17" s="54"/>
+      <c r="AC17" s="54"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="54"/>
+      <c r="AF17" s="54"/>
+      <c r="AG17" s="54"/>
+      <c r="AH17" s="54"/>
+      <c r="AI17" s="54"/>
+      <c r="AJ17" s="54"/>
+      <c r="AK17" s="54"/>
+      <c r="AL17" s="54"/>
+      <c r="AM17" s="54"/>
+      <c r="AN17" s="118"/>
     </row>
     <row r="18" spans="1:40" customHeight="1" ht="17">
-      <c r="A18" s="100"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="140"/>
-      <c r="H18" s="140"/>
-      <c r="I18" s="140"/>
-      <c r="J18" s="140"/>
-      <c r="K18" s="140"/>
-      <c r="L18" s="140"/>
-      <c r="M18" s="140"/>
-      <c r="N18" s="140"/>
-      <c r="O18" s="140"/>
-      <c r="P18" s="140"/>
-      <c r="Q18" s="140"/>
-      <c r="R18" s="140"/>
-      <c r="S18" s="142"/>
-      <c r="T18" s="47"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="51"/>
-      <c r="Y18" s="52" t="s">
+      <c r="A18" s="101"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="141"/>
+      <c r="I18" s="141"/>
+      <c r="J18" s="141"/>
+      <c r="K18" s="141"/>
+      <c r="L18" s="141"/>
+      <c r="M18" s="141"/>
+      <c r="N18" s="141"/>
+      <c r="O18" s="141"/>
+      <c r="P18" s="141"/>
+      <c r="Q18" s="141"/>
+      <c r="R18" s="141"/>
+      <c r="S18" s="143"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="50"/>
+      <c r="V18" s="50"/>
+      <c r="W18" s="50"/>
+      <c r="X18" s="52"/>
+      <c r="Y18" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="Z18" s="53"/>
-      <c r="AA18" s="53"/>
-      <c r="AB18" s="53"/>
-      <c r="AC18" s="53"/>
-      <c r="AD18" s="53"/>
-      <c r="AE18" s="53"/>
-      <c r="AF18" s="53"/>
-      <c r="AG18" s="53"/>
-      <c r="AH18" s="53"/>
-      <c r="AI18" s="53"/>
-      <c r="AJ18" s="53"/>
-      <c r="AK18" s="53"/>
-      <c r="AL18" s="53"/>
-      <c r="AM18" s="53"/>
-      <c r="AN18" s="117"/>
+      <c r="Z18" s="54"/>
+      <c r="AA18" s="54"/>
+      <c r="AB18" s="54"/>
+      <c r="AC18" s="54"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="54"/>
+      <c r="AF18" s="54"/>
+      <c r="AG18" s="54"/>
+      <c r="AH18" s="54"/>
+      <c r="AI18" s="54"/>
+      <c r="AJ18" s="54"/>
+      <c r="AK18" s="54"/>
+      <c r="AL18" s="54"/>
+      <c r="AM18" s="54"/>
+      <c r="AN18" s="118"/>
     </row>
     <row r="19" spans="1:40" customHeight="1" ht="17">
-      <c r="A19" s="97" t="s">
+      <c r="A19" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="54">
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="55">
         <v>0</v>
       </c>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="40"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="35" t="s">
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="42"/>
+      <c r="T19" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="U19" s="36"/>
-      <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="37"/>
-      <c r="Y19" s="54">
+      <c r="U19" s="37"/>
+      <c r="V19" s="37"/>
+      <c r="W19" s="37"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="55">
         <v>0</v>
       </c>
-      <c r="Z19" s="40"/>
-      <c r="AA19" s="40"/>
-      <c r="AB19" s="40"/>
-      <c r="AC19" s="40"/>
-      <c r="AD19" s="40"/>
-      <c r="AE19" s="40"/>
-      <c r="AF19" s="40"/>
-      <c r="AG19" s="40"/>
-      <c r="AH19" s="40"/>
-      <c r="AI19" s="40"/>
-      <c r="AJ19" s="40"/>
-      <c r="AK19" s="40"/>
-      <c r="AL19" s="40"/>
-      <c r="AM19" s="40"/>
-      <c r="AN19" s="116"/>
+      <c r="Z19" s="41"/>
+      <c r="AA19" s="41"/>
+      <c r="AB19" s="41"/>
+      <c r="AC19" s="41"/>
+      <c r="AD19" s="41"/>
+      <c r="AE19" s="41"/>
+      <c r="AF19" s="41"/>
+      <c r="AG19" s="41"/>
+      <c r="AH19" s="41"/>
+      <c r="AI19" s="41"/>
+      <c r="AJ19" s="41"/>
+      <c r="AK19" s="41"/>
+      <c r="AL19" s="41"/>
+      <c r="AM19" s="41"/>
+      <c r="AN19" s="117"/>
     </row>
     <row r="20" spans="1:40" customHeight="1" ht="30">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="55" t="s">
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="U20" s="56"/>
-      <c r="V20" s="56"/>
-      <c r="W20" s="56"/>
-      <c r="X20" s="57"/>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
-      <c r="AH20" s="24"/>
-      <c r="AI20" s="24"/>
-      <c r="AJ20" s="24"/>
-      <c r="AK20" s="24"/>
-      <c r="AL20" s="24"/>
-      <c r="AM20" s="24"/>
-      <c r="AN20" s="111"/>
+      <c r="U20" s="57"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="58"/>
+      <c r="Y20" s="40"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="25"/>
+      <c r="AH20" s="25"/>
+      <c r="AI20" s="25"/>
+      <c r="AJ20" s="25"/>
+      <c r="AK20" s="25"/>
+      <c r="AL20" s="25"/>
+      <c r="AM20" s="25"/>
+      <c r="AN20" s="112"/>
     </row>
     <row r="21" spans="1:40" customHeight="1" ht="15">
-      <c r="A21" s="101" t="s">
+      <c r="A21" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="58"/>
-      <c r="S21" s="58"/>
-      <c r="T21" s="58"/>
-      <c r="U21" s="58"/>
-      <c r="V21" s="58"/>
-      <c r="W21" s="58"/>
-      <c r="X21" s="58"/>
-      <c r="Y21" s="58"/>
-      <c r="Z21" s="58"/>
-      <c r="AA21" s="58"/>
-      <c r="AB21" s="58"/>
-      <c r="AC21" s="58"/>
-      <c r="AD21" s="58"/>
-      <c r="AE21" s="58"/>
-      <c r="AF21" s="58"/>
-      <c r="AG21" s="58"/>
-      <c r="AH21" s="58"/>
-      <c r="AI21" s="58"/>
-      <c r="AJ21" s="58"/>
-      <c r="AK21" s="58"/>
-      <c r="AL21" s="58"/>
-      <c r="AM21" s="58"/>
-      <c r="AN21" s="118"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="59"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="59"/>
+      <c r="R21" s="59"/>
+      <c r="S21" s="59"/>
+      <c r="T21" s="59"/>
+      <c r="U21" s="59"/>
+      <c r="V21" s="59"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="59"/>
+      <c r="Y21" s="59"/>
+      <c r="Z21" s="59"/>
+      <c r="AA21" s="59"/>
+      <c r="AB21" s="59"/>
+      <c r="AC21" s="59"/>
+      <c r="AD21" s="59"/>
+      <c r="AE21" s="59"/>
+      <c r="AF21" s="59"/>
+      <c r="AG21" s="59"/>
+      <c r="AH21" s="59"/>
+      <c r="AI21" s="59"/>
+      <c r="AJ21" s="59"/>
+      <c r="AK21" s="59"/>
+      <c r="AL21" s="59"/>
+      <c r="AM21" s="59"/>
+      <c r="AN21" s="119"/>
     </row>
     <row r="22" spans="1:40" customHeight="1" ht="33.6">
-      <c r="A22" s="101" t="s">
+      <c r="A22" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="58"/>
-      <c r="S22" s="58"/>
-      <c r="T22" s="58"/>
-      <c r="U22" s="58"/>
-      <c r="V22" s="58"/>
-      <c r="W22" s="58"/>
-      <c r="X22" s="58"/>
-      <c r="Y22" s="58"/>
-      <c r="Z22" s="58"/>
-      <c r="AA22" s="58"/>
-      <c r="AB22" s="58"/>
-      <c r="AC22" s="58"/>
-      <c r="AD22" s="58"/>
-      <c r="AE22" s="58"/>
-      <c r="AF22" s="58"/>
-      <c r="AG22" s="58"/>
-      <c r="AH22" s="58"/>
-      <c r="AI22" s="58"/>
-      <c r="AJ22" s="58"/>
-      <c r="AK22" s="58"/>
-      <c r="AL22" s="58"/>
-      <c r="AM22" s="58"/>
-      <c r="AN22" s="118"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="59"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="59"/>
+      <c r="R22" s="59"/>
+      <c r="S22" s="59"/>
+      <c r="T22" s="59"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="59"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="59"/>
+      <c r="Y22" s="59"/>
+      <c r="Z22" s="59"/>
+      <c r="AA22" s="59"/>
+      <c r="AB22" s="59"/>
+      <c r="AC22" s="59"/>
+      <c r="AD22" s="59"/>
+      <c r="AE22" s="59"/>
+      <c r="AF22" s="59"/>
+      <c r="AG22" s="59"/>
+      <c r="AH22" s="59"/>
+      <c r="AI22" s="59"/>
+      <c r="AJ22" s="59"/>
+      <c r="AK22" s="59"/>
+      <c r="AL22" s="59"/>
+      <c r="AM22" s="59"/>
+      <c r="AN22" s="119"/>
     </row>
     <row r="23" spans="1:40" customHeight="1" ht="24.6">
-      <c r="A23" s="101" t="s">
+      <c r="A23" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="58"/>
-      <c r="T23" s="58"/>
-      <c r="U23" s="58"/>
-      <c r="V23" s="58"/>
-      <c r="W23" s="58"/>
-      <c r="X23" s="58"/>
-      <c r="Y23" s="58"/>
-      <c r="Z23" s="58"/>
-      <c r="AA23" s="58"/>
-      <c r="AB23" s="58"/>
-      <c r="AC23" s="58"/>
-      <c r="AD23" s="58"/>
-      <c r="AE23" s="58"/>
-      <c r="AF23" s="58"/>
-      <c r="AG23" s="58"/>
-      <c r="AH23" s="58"/>
-      <c r="AI23" s="58"/>
-      <c r="AJ23" s="58"/>
-      <c r="AK23" s="58"/>
-      <c r="AL23" s="58"/>
-      <c r="AM23" s="58"/>
-      <c r="AN23" s="118"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="59"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="59"/>
+      <c r="R23" s="59"/>
+      <c r="S23" s="59"/>
+      <c r="T23" s="59"/>
+      <c r="U23" s="59"/>
+      <c r="V23" s="59"/>
+      <c r="W23" s="59"/>
+      <c r="X23" s="59"/>
+      <c r="Y23" s="59"/>
+      <c r="Z23" s="59"/>
+      <c r="AA23" s="59"/>
+      <c r="AB23" s="59"/>
+      <c r="AC23" s="59"/>
+      <c r="AD23" s="59"/>
+      <c r="AE23" s="59"/>
+      <c r="AF23" s="59"/>
+      <c r="AG23" s="59"/>
+      <c r="AH23" s="59"/>
+      <c r="AI23" s="59"/>
+      <c r="AJ23" s="59"/>
+      <c r="AK23" s="59"/>
+      <c r="AL23" s="59"/>
+      <c r="AM23" s="59"/>
+      <c r="AN23" s="119"/>
     </row>
     <row r="24" spans="1:40" customHeight="1" ht="9.2">
-      <c r="A24" s="101" t="s">
+      <c r="A24" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="58"/>
-      <c r="S24" s="58"/>
-      <c r="T24" s="58"/>
-      <c r="U24" s="58"/>
-      <c r="V24" s="58"/>
-      <c r="W24" s="58"/>
-      <c r="X24" s="58"/>
-      <c r="Y24" s="58"/>
-      <c r="Z24" s="58"/>
-      <c r="AA24" s="58"/>
-      <c r="AB24" s="58"/>
-      <c r="AC24" s="58"/>
-      <c r="AD24" s="58"/>
-      <c r="AE24" s="58"/>
-      <c r="AF24" s="58"/>
-      <c r="AG24" s="58"/>
-      <c r="AH24" s="58"/>
-      <c r="AI24" s="58"/>
-      <c r="AJ24" s="58"/>
-      <c r="AK24" s="58"/>
-      <c r="AL24" s="58"/>
-      <c r="AM24" s="58"/>
-      <c r="AN24" s="118"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="59"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="59"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="59"/>
+      <c r="R24" s="59"/>
+      <c r="S24" s="59"/>
+      <c r="T24" s="59"/>
+      <c r="U24" s="59"/>
+      <c r="V24" s="59"/>
+      <c r="W24" s="59"/>
+      <c r="X24" s="59"/>
+      <c r="Y24" s="59"/>
+      <c r="Z24" s="59"/>
+      <c r="AA24" s="59"/>
+      <c r="AB24" s="59"/>
+      <c r="AC24" s="59"/>
+      <c r="AD24" s="59"/>
+      <c r="AE24" s="59"/>
+      <c r="AF24" s="59"/>
+      <c r="AG24" s="59"/>
+      <c r="AH24" s="59"/>
+      <c r="AI24" s="59"/>
+      <c r="AJ24" s="59"/>
+      <c r="AK24" s="59"/>
+      <c r="AL24" s="59"/>
+      <c r="AM24" s="59"/>
+      <c r="AN24" s="119"/>
     </row>
     <row r="25" spans="1:40" customHeight="1" ht="18.4">
-      <c r="A25" s="101" t="s">
+      <c r="A25" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="58"/>
-      <c r="T25" s="58"/>
-      <c r="U25" s="58"/>
-      <c r="V25" s="58"/>
-      <c r="W25" s="58"/>
-      <c r="X25" s="58"/>
-      <c r="Y25" s="58"/>
-      <c r="Z25" s="58"/>
-      <c r="AA25" s="58"/>
-      <c r="AB25" s="58"/>
-      <c r="AC25" s="58"/>
-      <c r="AD25" s="58"/>
-      <c r="AE25" s="58"/>
-      <c r="AF25" s="58"/>
-      <c r="AG25" s="58"/>
-      <c r="AH25" s="58"/>
-      <c r="AI25" s="58"/>
-      <c r="AJ25" s="58"/>
-      <c r="AK25" s="58"/>
-      <c r="AL25" s="58"/>
-      <c r="AM25" s="58"/>
-      <c r="AN25" s="118"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="59"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="59"/>
+      <c r="R25" s="59"/>
+      <c r="S25" s="59"/>
+      <c r="T25" s="59"/>
+      <c r="U25" s="59"/>
+      <c r="V25" s="59"/>
+      <c r="W25" s="59"/>
+      <c r="X25" s="59"/>
+      <c r="Y25" s="59"/>
+      <c r="Z25" s="59"/>
+      <c r="AA25" s="59"/>
+      <c r="AB25" s="59"/>
+      <c r="AC25" s="59"/>
+      <c r="AD25" s="59"/>
+      <c r="AE25" s="59"/>
+      <c r="AF25" s="59"/>
+      <c r="AG25" s="59"/>
+      <c r="AH25" s="59"/>
+      <c r="AI25" s="59"/>
+      <c r="AJ25" s="59"/>
+      <c r="AK25" s="59"/>
+      <c r="AL25" s="59"/>
+      <c r="AM25" s="59"/>
+      <c r="AN25" s="119"/>
     </row>
     <row r="26" spans="1:40" customHeight="1" ht="36.8">
-      <c r="A26" s="101" t="s">
+      <c r="A26" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="58"/>
-      <c r="S26" s="58"/>
-      <c r="T26" s="58"/>
-      <c r="U26" s="58"/>
-      <c r="V26" s="58"/>
-      <c r="W26" s="58"/>
-      <c r="X26" s="58"/>
-      <c r="Y26" s="58"/>
-      <c r="Z26" s="58"/>
-      <c r="AA26" s="58"/>
-      <c r="AB26" s="58"/>
-      <c r="AC26" s="58"/>
-      <c r="AD26" s="58"/>
-      <c r="AE26" s="58"/>
-      <c r="AF26" s="58"/>
-      <c r="AG26" s="58"/>
-      <c r="AH26" s="58"/>
-      <c r="AI26" s="58"/>
-      <c r="AJ26" s="58"/>
-      <c r="AK26" s="58"/>
-      <c r="AL26" s="58"/>
-      <c r="AM26" s="58"/>
-      <c r="AN26" s="118"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="59"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="59"/>
+      <c r="R26" s="59"/>
+      <c r="S26" s="59"/>
+      <c r="T26" s="59"/>
+      <c r="U26" s="59"/>
+      <c r="V26" s="59"/>
+      <c r="W26" s="59"/>
+      <c r="X26" s="59"/>
+      <c r="Y26" s="59"/>
+      <c r="Z26" s="59"/>
+      <c r="AA26" s="59"/>
+      <c r="AB26" s="59"/>
+      <c r="AC26" s="59"/>
+      <c r="AD26" s="59"/>
+      <c r="AE26" s="59"/>
+      <c r="AF26" s="59"/>
+      <c r="AG26" s="59"/>
+      <c r="AH26" s="59"/>
+      <c r="AI26" s="59"/>
+      <c r="AJ26" s="59"/>
+      <c r="AK26" s="59"/>
+      <c r="AL26" s="59"/>
+      <c r="AM26" s="59"/>
+      <c r="AN26" s="119"/>
     </row>
     <row r="27" spans="1:40" customHeight="1" ht="22.8">
-      <c r="A27" s="101" t="s">
+      <c r="A27" s="102" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="58"/>
-      <c r="R27" s="58"/>
-      <c r="S27" s="58"/>
-      <c r="T27" s="58"/>
-      <c r="U27" s="58"/>
-      <c r="V27" s="58"/>
-      <c r="W27" s="58"/>
-      <c r="X27" s="58"/>
-      <c r="Y27" s="58"/>
-      <c r="Z27" s="58"/>
-      <c r="AA27" s="58"/>
-      <c r="AB27" s="58"/>
-      <c r="AC27" s="58"/>
-      <c r="AD27" s="58"/>
-      <c r="AE27" s="58"/>
-      <c r="AF27" s="58"/>
-      <c r="AG27" s="58"/>
-      <c r="AH27" s="58"/>
-      <c r="AI27" s="58"/>
-      <c r="AJ27" s="58"/>
-      <c r="AK27" s="58"/>
-      <c r="AL27" s="58"/>
-      <c r="AM27" s="58"/>
-      <c r="AN27" s="118"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="59"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="59"/>
+      <c r="R27" s="59"/>
+      <c r="S27" s="59"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="59"/>
+      <c r="V27" s="59"/>
+      <c r="W27" s="59"/>
+      <c r="X27" s="59"/>
+      <c r="Y27" s="59"/>
+      <c r="Z27" s="59"/>
+      <c r="AA27" s="59"/>
+      <c r="AB27" s="59"/>
+      <c r="AC27" s="59"/>
+      <c r="AD27" s="59"/>
+      <c r="AE27" s="59"/>
+      <c r="AF27" s="59"/>
+      <c r="AG27" s="59"/>
+      <c r="AH27" s="59"/>
+      <c r="AI27" s="59"/>
+      <c r="AJ27" s="59"/>
+      <c r="AK27" s="59"/>
+      <c r="AL27" s="59"/>
+      <c r="AM27" s="59"/>
+      <c r="AN27" s="119"/>
     </row>
     <row r="28" spans="1:40" customHeight="1" ht="21">
-      <c r="A28" s="101" t="s">
+      <c r="A28" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="58"/>
-      <c r="R28" s="58"/>
-      <c r="S28" s="58"/>
-      <c r="T28" s="58"/>
-      <c r="U28" s="58"/>
-      <c r="V28" s="58"/>
-      <c r="W28" s="58"/>
-      <c r="X28" s="58"/>
-      <c r="Y28" s="58"/>
-      <c r="Z28" s="58"/>
-      <c r="AA28" s="58"/>
-      <c r="AB28" s="58"/>
-      <c r="AC28" s="58"/>
-      <c r="AD28" s="58"/>
-      <c r="AE28" s="58"/>
-      <c r="AF28" s="58"/>
-      <c r="AG28" s="58"/>
-      <c r="AH28" s="58"/>
-      <c r="AI28" s="58"/>
-      <c r="AJ28" s="58"/>
-      <c r="AK28" s="58"/>
-      <c r="AL28" s="58"/>
-      <c r="AM28" s="58"/>
-      <c r="AN28" s="118"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="59"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="59"/>
+      <c r="R28" s="59"/>
+      <c r="S28" s="59"/>
+      <c r="T28" s="59"/>
+      <c r="U28" s="59"/>
+      <c r="V28" s="59"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="59"/>
+      <c r="Y28" s="59"/>
+      <c r="Z28" s="59"/>
+      <c r="AA28" s="59"/>
+      <c r="AB28" s="59"/>
+      <c r="AC28" s="59"/>
+      <c r="AD28" s="59"/>
+      <c r="AE28" s="59"/>
+      <c r="AF28" s="59"/>
+      <c r="AG28" s="59"/>
+      <c r="AH28" s="59"/>
+      <c r="AI28" s="59"/>
+      <c r="AJ28" s="59"/>
+      <c r="AK28" s="59"/>
+      <c r="AL28" s="59"/>
+      <c r="AM28" s="59"/>
+      <c r="AN28" s="119"/>
     </row>
     <row r="29" spans="1:40" customHeight="1" ht="12">
-      <c r="A29" s="101" t="s">
+      <c r="A29" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="58"/>
-      <c r="S29" s="58"/>
-      <c r="T29" s="58"/>
-      <c r="U29" s="58"/>
-      <c r="V29" s="58"/>
-      <c r="W29" s="58"/>
-      <c r="X29" s="58"/>
-      <c r="Y29" s="58"/>
-      <c r="Z29" s="58"/>
-      <c r="AA29" s="58"/>
-      <c r="AB29" s="58"/>
-      <c r="AC29" s="58"/>
-      <c r="AD29" s="58"/>
-      <c r="AE29" s="58"/>
-      <c r="AF29" s="58"/>
-      <c r="AG29" s="58"/>
-      <c r="AH29" s="58"/>
-      <c r="AI29" s="58"/>
-      <c r="AJ29" s="58"/>
-      <c r="AK29" s="58"/>
-      <c r="AL29" s="58"/>
-      <c r="AM29" s="58"/>
-      <c r="AN29" s="118"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="59"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="59"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="59"/>
+      <c r="R29" s="59"/>
+      <c r="S29" s="59"/>
+      <c r="T29" s="59"/>
+      <c r="U29" s="59"/>
+      <c r="V29" s="59"/>
+      <c r="W29" s="59"/>
+      <c r="X29" s="59"/>
+      <c r="Y29" s="59"/>
+      <c r="Z29" s="59"/>
+      <c r="AA29" s="59"/>
+      <c r="AB29" s="59"/>
+      <c r="AC29" s="59"/>
+      <c r="AD29" s="59"/>
+      <c r="AE29" s="59"/>
+      <c r="AF29" s="59"/>
+      <c r="AG29" s="59"/>
+      <c r="AH29" s="59"/>
+      <c r="AI29" s="59"/>
+      <c r="AJ29" s="59"/>
+      <c r="AK29" s="59"/>
+      <c r="AL29" s="59"/>
+      <c r="AM29" s="59"/>
+      <c r="AN29" s="119"/>
     </row>
     <row r="30" spans="1:40" customHeight="1" ht="14.4">
-      <c r="A30" s="101" t="s">
+      <c r="A30" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="58"/>
-      <c r="O30" s="58"/>
-      <c r="P30" s="58"/>
-      <c r="Q30" s="58"/>
-      <c r="R30" s="58"/>
-      <c r="S30" s="58"/>
-      <c r="T30" s="58"/>
-      <c r="U30" s="58"/>
-      <c r="V30" s="58"/>
-      <c r="W30" s="58"/>
-      <c r="X30" s="58"/>
-      <c r="Y30" s="58"/>
-      <c r="Z30" s="58"/>
-      <c r="AA30" s="58"/>
-      <c r="AB30" s="58"/>
-      <c r="AC30" s="58"/>
-      <c r="AD30" s="58"/>
-      <c r="AE30" s="58"/>
-      <c r="AF30" s="58"/>
-      <c r="AG30" s="58"/>
-      <c r="AH30" s="58"/>
-      <c r="AI30" s="58"/>
-      <c r="AJ30" s="58"/>
-      <c r="AK30" s="58"/>
-      <c r="AL30" s="58"/>
-      <c r="AM30" s="58"/>
-      <c r="AN30" s="118"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="59"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="59"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="59"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="59"/>
+      <c r="R30" s="59"/>
+      <c r="S30" s="59"/>
+      <c r="T30" s="59"/>
+      <c r="U30" s="59"/>
+      <c r="V30" s="59"/>
+      <c r="W30" s="59"/>
+      <c r="X30" s="59"/>
+      <c r="Y30" s="59"/>
+      <c r="Z30" s="59"/>
+      <c r="AA30" s="59"/>
+      <c r="AB30" s="59"/>
+      <c r="AC30" s="59"/>
+      <c r="AD30" s="59"/>
+      <c r="AE30" s="59"/>
+      <c r="AF30" s="59"/>
+      <c r="AG30" s="59"/>
+      <c r="AH30" s="59"/>
+      <c r="AI30" s="59"/>
+      <c r="AJ30" s="59"/>
+      <c r="AK30" s="59"/>
+      <c r="AL30" s="59"/>
+      <c r="AM30" s="59"/>
+      <c r="AN30" s="119"/>
     </row>
     <row r="31" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A31" s="102"/>
+      <c r="A31" s="103"/>
       <c r="B31"/>
       <c r="C31"/>
-      <c r="D31" s="67" t="s">
+      <c r="D31" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="71"/>
-      <c r="V31" s="71"/>
-      <c r="W31" s="73"/>
-      <c r="X31" s="77" t="s">
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
+      <c r="T31" s="72"/>
+      <c r="U31" s="72"/>
+      <c r="V31" s="72"/>
+      <c r="W31" s="74"/>
+      <c r="X31" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="Y31" s="79"/>
-      <c r="Z31" s="79"/>
-      <c r="AA31" s="79"/>
-      <c r="AB31" s="79"/>
-      <c r="AC31" s="79"/>
-      <c r="AD31" s="81"/>
-      <c r="AE31" s="83">
+      <c r="Y31" s="80"/>
+      <c r="Z31" s="80"/>
+      <c r="AA31" s="80"/>
+      <c r="AB31" s="80"/>
+      <c r="AC31" s="80"/>
+      <c r="AD31" s="82"/>
+      <c r="AE31" s="84">
         <v>0</v>
       </c>
-      <c r="AF31" s="85"/>
-      <c r="AG31" s="85"/>
-      <c r="AH31" s="85"/>
-      <c r="AI31" s="85"/>
-      <c r="AJ31" s="85"/>
-      <c r="AK31" s="85"/>
-      <c r="AL31" s="85"/>
-      <c r="AM31" s="87"/>
-      <c r="AN31" s="119"/>
+      <c r="AF31" s="86"/>
+      <c r="AG31" s="86"/>
+      <c r="AH31" s="86"/>
+      <c r="AI31" s="86"/>
+      <c r="AJ31" s="86"/>
+      <c r="AK31" s="86"/>
+      <c r="AL31" s="86"/>
+      <c r="AM31" s="88"/>
+      <c r="AN31" s="120"/>
     </row>
     <row r="32" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A32" s="102"/>
+      <c r="A32" s="103"/>
       <c r="B32"/>
       <c r="C32"/>
-      <c r="D32" s="68" t="s">
+      <c r="D32" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59"/>
-      <c r="L32" s="59"/>
-      <c r="M32" s="59"/>
-      <c r="N32" s="59"/>
-      <c r="O32" s="59"/>
-      <c r="P32" s="59"/>
-      <c r="Q32" s="59"/>
-      <c r="R32" s="59"/>
-      <c r="S32" s="59"/>
-      <c r="T32" s="59"/>
-      <c r="U32" s="59"/>
-      <c r="V32" s="59"/>
-      <c r="W32" s="74"/>
-      <c r="X32" s="78"/>
-      <c r="Y32" s="80"/>
-      <c r="Z32" s="80"/>
-      <c r="AA32" s="80"/>
-      <c r="AB32" s="80"/>
-      <c r="AC32" s="80"/>
-      <c r="AD32" s="82"/>
-      <c r="AE32" s="84"/>
-      <c r="AF32" s="86"/>
-      <c r="AG32" s="86"/>
-      <c r="AH32" s="86"/>
-      <c r="AI32" s="86"/>
-      <c r="AJ32" s="86"/>
-      <c r="AK32" s="86"/>
-      <c r="AL32" s="86"/>
-      <c r="AM32" s="88"/>
-      <c r="AN32" s="119"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="60"/>
+      <c r="S32" s="60"/>
+      <c r="T32" s="60"/>
+      <c r="U32" s="60"/>
+      <c r="V32" s="60"/>
+      <c r="W32" s="75"/>
+      <c r="X32" s="79"/>
+      <c r="Y32" s="81"/>
+      <c r="Z32" s="81"/>
+      <c r="AA32" s="81"/>
+      <c r="AB32" s="81"/>
+      <c r="AC32" s="81"/>
+      <c r="AD32" s="83"/>
+      <c r="AE32" s="85"/>
+      <c r="AF32" s="87"/>
+      <c r="AG32" s="87"/>
+      <c r="AH32" s="87"/>
+      <c r="AI32" s="87"/>
+      <c r="AJ32" s="87"/>
+      <c r="AK32" s="87"/>
+      <c r="AL32" s="87"/>
+      <c r="AM32" s="89"/>
+      <c r="AN32" s="120"/>
     </row>
     <row r="33" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A33" s="102"/>
+      <c r="A33" s="103"/>
       <c r="B33"/>
       <c r="C33"/>
-      <c r="D33" s="69" t="s">
+      <c r="D33" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="60"/>
-      <c r="J33" s="60"/>
-      <c r="K33" s="60"/>
-      <c r="L33" s="60"/>
-      <c r="M33" s="60"/>
-      <c r="N33" s="60"/>
-      <c r="O33" s="60"/>
-      <c r="P33" s="60"/>
-      <c r="Q33" s="60"/>
-      <c r="R33" s="60"/>
-      <c r="S33" s="60"/>
-      <c r="T33" s="60"/>
-      <c r="U33" s="60"/>
-      <c r="V33" s="60"/>
-      <c r="W33" s="75"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="61"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="61"/>
+      <c r="P33" s="61"/>
+      <c r="Q33" s="61"/>
+      <c r="R33" s="61"/>
+      <c r="S33" s="61"/>
+      <c r="T33" s="61"/>
+      <c r="U33" s="61"/>
+      <c r="V33" s="61"/>
+      <c r="W33" s="76"/>
       <c r="X33"/>
       <c r="Y33"/>
       <c r="Z33"/>
@@ -2951,258 +2957,258 @@
       <c r="AK33"/>
       <c r="AL33"/>
       <c r="AM33"/>
-      <c r="AN33" s="119"/>
+      <c r="AN33" s="120"/>
     </row>
     <row r="34" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A34" s="102"/>
-      <c r="B34" s="61" t="s">
+      <c r="A34" s="103"/>
+      <c r="B34" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="68" t="s">
+      <c r="C34" s="65"/>
+      <c r="D34" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="59"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="59"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="59"/>
-      <c r="M34" s="59"/>
-      <c r="N34" s="59"/>
-      <c r="O34" s="59"/>
-      <c r="P34" s="59"/>
-      <c r="Q34" s="59"/>
-      <c r="R34" s="59"/>
-      <c r="S34" s="59"/>
-      <c r="T34" s="59"/>
-      <c r="U34" s="59"/>
-      <c r="V34" s="59"/>
-      <c r="W34" s="74"/>
-      <c r="X34" s="89" t="s">
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="60"/>
+      <c r="M34" s="60"/>
+      <c r="N34" s="60"/>
+      <c r="O34" s="60"/>
+      <c r="P34" s="60"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="60"/>
+      <c r="S34" s="60"/>
+      <c r="T34" s="60"/>
+      <c r="U34" s="60"/>
+      <c r="V34" s="60"/>
+      <c r="W34" s="75"/>
+      <c r="X34" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="Y34" s="89"/>
-      <c r="Z34" s="89"/>
-      <c r="AA34" s="89"/>
-      <c r="AB34" s="89"/>
-      <c r="AC34" s="89"/>
-      <c r="AD34" s="89"/>
-      <c r="AE34" s="89"/>
-      <c r="AF34" s="89"/>
-      <c r="AG34" s="89"/>
-      <c r="AH34" s="89"/>
-      <c r="AI34" s="89"/>
-      <c r="AJ34" s="89"/>
-      <c r="AK34" s="89"/>
-      <c r="AL34" s="89"/>
-      <c r="AM34" s="89"/>
-      <c r="AN34" s="120"/>
+      <c r="Y34" s="90"/>
+      <c r="Z34" s="90"/>
+      <c r="AA34" s="90"/>
+      <c r="AB34" s="90"/>
+      <c r="AC34" s="90"/>
+      <c r="AD34" s="90"/>
+      <c r="AE34" s="90"/>
+      <c r="AF34" s="90"/>
+      <c r="AG34" s="90"/>
+      <c r="AH34" s="90"/>
+      <c r="AI34" s="90"/>
+      <c r="AJ34" s="90"/>
+      <c r="AK34" s="90"/>
+      <c r="AL34" s="90"/>
+      <c r="AM34" s="90"/>
+      <c r="AN34" s="121"/>
     </row>
     <row r="35" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A35" s="102"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="65"/>
-      <c r="D35" s="68" t="s">
+      <c r="A35" s="103"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="59"/>
-      <c r="J35" s="59"/>
-      <c r="K35" s="59"/>
-      <c r="L35" s="59"/>
-      <c r="M35" s="59"/>
-      <c r="N35" s="59"/>
-      <c r="O35" s="59"/>
-      <c r="P35" s="59"/>
-      <c r="Q35" s="59"/>
-      <c r="R35" s="59"/>
-      <c r="S35" s="59"/>
-      <c r="T35" s="59"/>
-      <c r="U35" s="59"/>
-      <c r="V35" s="59"/>
-      <c r="W35" s="74"/>
-      <c r="X35" s="89"/>
-      <c r="Y35" s="89"/>
-      <c r="Z35" s="89"/>
-      <c r="AA35" s="89"/>
-      <c r="AB35" s="89"/>
-      <c r="AC35" s="89"/>
-      <c r="AD35" s="89"/>
-      <c r="AE35" s="89"/>
-      <c r="AF35" s="89"/>
-      <c r="AG35" s="89"/>
-      <c r="AH35" s="89"/>
-      <c r="AI35" s="89"/>
-      <c r="AJ35" s="89"/>
-      <c r="AK35" s="89"/>
-      <c r="AL35" s="89"/>
-      <c r="AM35" s="89"/>
-      <c r="AN35" s="120"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="60"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="60"/>
+      <c r="M35" s="60"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="60"/>
+      <c r="P35" s="60"/>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="60"/>
+      <c r="S35" s="60"/>
+      <c r="T35" s="60"/>
+      <c r="U35" s="60"/>
+      <c r="V35" s="60"/>
+      <c r="W35" s="75"/>
+      <c r="X35" s="90"/>
+      <c r="Y35" s="90"/>
+      <c r="Z35" s="90"/>
+      <c r="AA35" s="90"/>
+      <c r="AB35" s="90"/>
+      <c r="AC35" s="90"/>
+      <c r="AD35" s="90"/>
+      <c r="AE35" s="90"/>
+      <c r="AF35" s="90"/>
+      <c r="AG35" s="90"/>
+      <c r="AH35" s="90"/>
+      <c r="AI35" s="90"/>
+      <c r="AJ35" s="90"/>
+      <c r="AK35" s="90"/>
+      <c r="AL35" s="90"/>
+      <c r="AM35" s="90"/>
+      <c r="AN35" s="121"/>
     </row>
     <row r="36" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A36" s="102"/>
-      <c r="B36" s="62"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="68" t="s">
+      <c r="A36" s="103"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
-      <c r="J36" s="59"/>
-      <c r="K36" s="59"/>
-      <c r="L36" s="59"/>
-      <c r="M36" s="59"/>
-      <c r="N36" s="59"/>
-      <c r="O36" s="59"/>
-      <c r="P36" s="59"/>
-      <c r="Q36" s="59"/>
-      <c r="R36" s="59"/>
-      <c r="S36" s="59"/>
-      <c r="T36" s="59"/>
-      <c r="U36" s="59"/>
-      <c r="V36" s="59"/>
-      <c r="W36" s="74"/>
-      <c r="X36" s="89"/>
-      <c r="Y36" s="89"/>
-      <c r="Z36" s="89"/>
-      <c r="AA36" s="89"/>
-      <c r="AB36" s="89"/>
-      <c r="AC36" s="89"/>
-      <c r="AD36" s="89"/>
-      <c r="AE36" s="89"/>
-      <c r="AF36" s="89"/>
-      <c r="AG36" s="89"/>
-      <c r="AH36" s="89"/>
-      <c r="AI36" s="89"/>
-      <c r="AJ36" s="89"/>
-      <c r="AK36" s="89"/>
-      <c r="AL36" s="89"/>
-      <c r="AM36" s="89"/>
-      <c r="AN36" s="120"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="60"/>
+      <c r="K36" s="60"/>
+      <c r="L36" s="60"/>
+      <c r="M36" s="60"/>
+      <c r="N36" s="60"/>
+      <c r="O36" s="60"/>
+      <c r="P36" s="60"/>
+      <c r="Q36" s="60"/>
+      <c r="R36" s="60"/>
+      <c r="S36" s="60"/>
+      <c r="T36" s="60"/>
+      <c r="U36" s="60"/>
+      <c r="V36" s="60"/>
+      <c r="W36" s="75"/>
+      <c r="X36" s="90"/>
+      <c r="Y36" s="90"/>
+      <c r="Z36" s="90"/>
+      <c r="AA36" s="90"/>
+      <c r="AB36" s="90"/>
+      <c r="AC36" s="90"/>
+      <c r="AD36" s="90"/>
+      <c r="AE36" s="90"/>
+      <c r="AF36" s="90"/>
+      <c r="AG36" s="90"/>
+      <c r="AH36" s="90"/>
+      <c r="AI36" s="90"/>
+      <c r="AJ36" s="90"/>
+      <c r="AK36" s="90"/>
+      <c r="AL36" s="90"/>
+      <c r="AM36" s="90"/>
+      <c r="AN36" s="121"/>
     </row>
     <row r="37" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A37" s="102"/>
-      <c r="B37" s="62"/>
-      <c r="C37" s="65"/>
-      <c r="D37" s="68" t="s">
+      <c r="A37" s="103"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="59"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="59"/>
-      <c r="M37" s="59"/>
-      <c r="N37" s="59"/>
-      <c r="O37" s="59"/>
-      <c r="P37" s="59"/>
-      <c r="Q37" s="59"/>
-      <c r="R37" s="59"/>
-      <c r="S37" s="59"/>
-      <c r="T37" s="59"/>
-      <c r="U37" s="59"/>
-      <c r="V37" s="59"/>
-      <c r="W37" s="74"/>
-      <c r="X37" s="89"/>
-      <c r="Y37" s="89"/>
-      <c r="Z37" s="89"/>
-      <c r="AA37" s="89"/>
-      <c r="AB37" s="89"/>
-      <c r="AC37" s="89"/>
-      <c r="AD37" s="89"/>
-      <c r="AE37" s="89"/>
-      <c r="AF37" s="89"/>
-      <c r="AG37" s="89"/>
-      <c r="AH37" s="89"/>
-      <c r="AI37" s="89"/>
-      <c r="AJ37" s="89"/>
-      <c r="AK37" s="89"/>
-      <c r="AL37" s="89"/>
-      <c r="AM37" s="89"/>
-      <c r="AN37" s="120"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="60"/>
+      <c r="M37" s="60"/>
+      <c r="N37" s="60"/>
+      <c r="O37" s="60"/>
+      <c r="P37" s="60"/>
+      <c r="Q37" s="60"/>
+      <c r="R37" s="60"/>
+      <c r="S37" s="60"/>
+      <c r="T37" s="60"/>
+      <c r="U37" s="60"/>
+      <c r="V37" s="60"/>
+      <c r="W37" s="75"/>
+      <c r="X37" s="90"/>
+      <c r="Y37" s="90"/>
+      <c r="Z37" s="90"/>
+      <c r="AA37" s="90"/>
+      <c r="AB37" s="90"/>
+      <c r="AC37" s="90"/>
+      <c r="AD37" s="90"/>
+      <c r="AE37" s="90"/>
+      <c r="AF37" s="90"/>
+      <c r="AG37" s="90"/>
+      <c r="AH37" s="90"/>
+      <c r="AI37" s="90"/>
+      <c r="AJ37" s="90"/>
+      <c r="AK37" s="90"/>
+      <c r="AL37" s="90"/>
+      <c r="AM37" s="90"/>
+      <c r="AN37" s="121"/>
     </row>
     <row r="38" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A38" s="102"/>
-      <c r="B38" s="62"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="69" t="s">
+      <c r="A38" s="103"/>
+      <c r="B38" s="63"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="E38" s="60"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="60"/>
-      <c r="H38" s="60"/>
-      <c r="I38" s="60"/>
-      <c r="J38" s="60"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="60"/>
-      <c r="N38" s="60"/>
-      <c r="O38" s="60"/>
-      <c r="P38" s="60"/>
-      <c r="Q38" s="60"/>
-      <c r="R38" s="60"/>
-      <c r="S38" s="60"/>
-      <c r="T38" s="60"/>
-      <c r="U38" s="60"/>
-      <c r="V38" s="60"/>
-      <c r="W38" s="75"/>
-      <c r="X38" s="89"/>
-      <c r="Y38" s="89"/>
-      <c r="Z38" s="89"/>
-      <c r="AA38" s="89"/>
-      <c r="AB38" s="89"/>
-      <c r="AC38" s="89"/>
-      <c r="AD38" s="89"/>
-      <c r="AE38" s="89"/>
-      <c r="AF38" s="89"/>
-      <c r="AG38" s="89"/>
-      <c r="AH38" s="89"/>
-      <c r="AI38" s="89"/>
-      <c r="AJ38" s="89"/>
-      <c r="AK38" s="89"/>
-      <c r="AL38" s="89"/>
-      <c r="AM38" s="89"/>
-      <c r="AN38" s="120"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="61"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="61"/>
+      <c r="S38" s="61"/>
+      <c r="T38" s="61"/>
+      <c r="U38" s="61"/>
+      <c r="V38" s="61"/>
+      <c r="W38" s="76"/>
+      <c r="X38" s="90"/>
+      <c r="Y38" s="90"/>
+      <c r="Z38" s="90"/>
+      <c r="AA38" s="90"/>
+      <c r="AB38" s="90"/>
+      <c r="AC38" s="90"/>
+      <c r="AD38" s="90"/>
+      <c r="AE38" s="90"/>
+      <c r="AF38" s="90"/>
+      <c r="AG38" s="90"/>
+      <c r="AH38" s="90"/>
+      <c r="AI38" s="90"/>
+      <c r="AJ38" s="90"/>
+      <c r="AK38" s="90"/>
+      <c r="AL38" s="90"/>
+      <c r="AM38" s="90"/>
+      <c r="AN38" s="121"/>
     </row>
     <row r="39" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A39" s="102"/>
-      <c r="B39" s="62"/>
-      <c r="C39" s="65"/>
-      <c r="D39" s="69" t="s">
+      <c r="A39" s="103"/>
+      <c r="B39" s="63"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="60"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="60"/>
-      <c r="M39" s="60"/>
-      <c r="N39" s="60"/>
-      <c r="O39" s="60"/>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="60"/>
-      <c r="S39" s="60"/>
-      <c r="T39" s="60"/>
-      <c r="U39" s="60"/>
-      <c r="V39" s="60"/>
-      <c r="W39" s="75"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="61"/>
+      <c r="O39" s="61"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="61"/>
+      <c r="S39" s="61"/>
+      <c r="T39" s="61"/>
+      <c r="U39" s="61"/>
+      <c r="V39" s="61"/>
+      <c r="W39" s="76"/>
       <c r="X39"/>
       <c r="Y39"/>
       <c r="Z39"/>
@@ -3219,34 +3225,34 @@
       <c r="AK39"/>
       <c r="AL39"/>
       <c r="AM39"/>
-      <c r="AN39" s="119"/>
+      <c r="AN39" s="120"/>
     </row>
     <row r="40" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A40" s="102"/>
-      <c r="B40" s="62"/>
-      <c r="C40" s="65"/>
-      <c r="D40" s="68" t="s">
+      <c r="A40" s="103"/>
+      <c r="B40" s="63"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59"/>
-      <c r="J40" s="59"/>
-      <c r="K40" s="59"/>
-      <c r="L40" s="59"/>
-      <c r="M40" s="59"/>
-      <c r="N40" s="59"/>
-      <c r="O40" s="59"/>
-      <c r="P40" s="59"/>
-      <c r="Q40" s="59"/>
-      <c r="R40" s="59"/>
-      <c r="S40" s="59"/>
-      <c r="T40" s="59"/>
-      <c r="U40" s="59"/>
-      <c r="V40" s="59"/>
-      <c r="W40" s="74"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="60"/>
+      <c r="N40" s="60"/>
+      <c r="O40" s="60"/>
+      <c r="P40" s="60"/>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="60"/>
+      <c r="S40" s="60"/>
+      <c r="T40" s="60"/>
+      <c r="U40" s="60"/>
+      <c r="V40" s="60"/>
+      <c r="W40" s="75"/>
       <c r="X40" s="2" t="s">
         <v>71</v>
       </c>
@@ -3265,34 +3271,34 @@
       <c r="AK40" s="2"/>
       <c r="AL40" s="2"/>
       <c r="AM40" s="2"/>
-      <c r="AN40" s="121"/>
+      <c r="AN40" s="122"/>
     </row>
     <row r="41" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A41" s="102"/>
-      <c r="B41" s="63"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="68" t="s">
+      <c r="A41" s="103"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="E41" s="59"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="59"/>
-      <c r="J41" s="59"/>
-      <c r="K41" s="59"/>
-      <c r="L41" s="59"/>
-      <c r="M41" s="59"/>
-      <c r="N41" s="59"/>
-      <c r="O41" s="59"/>
-      <c r="P41" s="59"/>
-      <c r="Q41" s="59"/>
-      <c r="R41" s="59"/>
-      <c r="S41" s="59"/>
-      <c r="T41" s="59"/>
-      <c r="U41" s="59"/>
-      <c r="V41" s="59"/>
-      <c r="W41" s="74"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="60"/>
+      <c r="V41" s="60"/>
+      <c r="W41" s="75"/>
       <c r="X41" s="2"/>
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
@@ -3309,34 +3315,34 @@
       <c r="AK41" s="2"/>
       <c r="AL41" s="2"/>
       <c r="AM41" s="2"/>
-      <c r="AN41" s="121"/>
+      <c r="AN41" s="122"/>
     </row>
     <row r="42" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A42" s="102"/>
+      <c r="A42" s="103"/>
       <c r="B42"/>
       <c r="C42"/>
-      <c r="D42" s="68" t="s">
+      <c r="D42" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="59"/>
-      <c r="J42" s="59"/>
-      <c r="K42" s="59"/>
-      <c r="L42" s="59"/>
-      <c r="M42" s="59"/>
-      <c r="N42" s="59"/>
-      <c r="O42" s="59"/>
-      <c r="P42" s="59"/>
-      <c r="Q42" s="59"/>
-      <c r="R42" s="59"/>
-      <c r="S42" s="59"/>
-      <c r="T42" s="59"/>
-      <c r="U42" s="59"/>
-      <c r="V42" s="59"/>
-      <c r="W42" s="74"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="60"/>
+      <c r="J42" s="60"/>
+      <c r="K42" s="60"/>
+      <c r="L42" s="60"/>
+      <c r="M42" s="60"/>
+      <c r="N42" s="60"/>
+      <c r="O42" s="60"/>
+      <c r="P42" s="60"/>
+      <c r="Q42" s="60"/>
+      <c r="R42" s="60"/>
+      <c r="S42" s="60"/>
+      <c r="T42" s="60"/>
+      <c r="U42" s="60"/>
+      <c r="V42" s="60"/>
+      <c r="W42" s="75"/>
       <c r="X42"/>
       <c r="Y42"/>
       <c r="Z42"/>
@@ -3353,34 +3359,34 @@
       <c r="AK42"/>
       <c r="AL42"/>
       <c r="AM42"/>
-      <c r="AN42" s="119"/>
+      <c r="AN42" s="120"/>
     </row>
     <row r="43" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A43" s="102"/>
+      <c r="A43" s="103"/>
       <c r="B43"/>
       <c r="C43"/>
-      <c r="D43" s="68" t="s">
+      <c r="D43" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
-      <c r="L43" s="59"/>
-      <c r="M43" s="59"/>
-      <c r="N43" s="59"/>
-      <c r="O43" s="59"/>
-      <c r="P43" s="59"/>
-      <c r="Q43" s="59"/>
-      <c r="R43" s="59"/>
-      <c r="S43" s="59"/>
-      <c r="T43" s="59"/>
-      <c r="U43" s="59"/>
-      <c r="V43" s="59"/>
-      <c r="W43" s="74"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="60"/>
+      <c r="H43" s="60"/>
+      <c r="I43" s="60"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="60"/>
+      <c r="L43" s="60"/>
+      <c r="M43" s="60"/>
+      <c r="N43" s="60"/>
+      <c r="O43" s="60"/>
+      <c r="P43" s="60"/>
+      <c r="Q43" s="60"/>
+      <c r="R43" s="60"/>
+      <c r="S43" s="60"/>
+      <c r="T43" s="60"/>
+      <c r="U43" s="60"/>
+      <c r="V43" s="60"/>
+      <c r="W43" s="75"/>
       <c r="X43"/>
       <c r="Y43"/>
       <c r="Z43"/>
@@ -3397,34 +3403,34 @@
       <c r="AK43"/>
       <c r="AL43"/>
       <c r="AM43"/>
-      <c r="AN43" s="119"/>
+      <c r="AN43" s="120"/>
     </row>
     <row r="44" spans="1:40" customHeight="1" ht="10.5">
-      <c r="A44" s="102"/>
+      <c r="A44" s="103"/>
       <c r="B44"/>
       <c r="C44"/>
-      <c r="D44" s="70" t="s">
+      <c r="D44" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="72"/>
-      <c r="H44" s="72"/>
-      <c r="I44" s="72"/>
-      <c r="J44" s="72"/>
-      <c r="K44" s="72"/>
-      <c r="L44" s="72"/>
-      <c r="M44" s="72"/>
-      <c r="N44" s="72"/>
-      <c r="O44" s="72"/>
-      <c r="P44" s="72"/>
-      <c r="Q44" s="72"/>
-      <c r="R44" s="72"/>
-      <c r="S44" s="72"/>
-      <c r="T44" s="72"/>
-      <c r="U44" s="72"/>
-      <c r="V44" s="72"/>
-      <c r="W44" s="76"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="73"/>
+      <c r="G44" s="73"/>
+      <c r="H44" s="73"/>
+      <c r="I44" s="73"/>
+      <c r="J44" s="73"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="73"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="73"/>
+      <c r="O44" s="73"/>
+      <c r="P44" s="73"/>
+      <c r="Q44" s="73"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="73"/>
+      <c r="T44" s="73"/>
+      <c r="U44" s="73"/>
+      <c r="V44" s="73"/>
+      <c r="W44" s="77"/>
       <c r="X44"/>
       <c r="Y44"/>
       <c r="Z44"/>
@@ -3441,10 +3447,10 @@
       <c r="AK44"/>
       <c r="AL44"/>
       <c r="AM44"/>
-      <c r="AN44" s="119"/>
+      <c r="AN44" s="120"/>
     </row>
     <row r="45" spans="1:40" customHeight="1" ht="20">
-      <c r="A45" s="103" t="s">
+      <c r="A45" s="104" t="s">
         <v>72</v>
       </c>
       <c r="B45" s="3"/>
@@ -3452,16 +3458,16 @@
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
+      <c r="G45" s="144"/>
+      <c r="H45" s="144"/>
+      <c r="I45" s="144"/>
+      <c r="J45" s="144"/>
+      <c r="K45" s="144"/>
+      <c r="L45" s="144"/>
+      <c r="M45" s="144"/>
+      <c r="N45" s="144"/>
+      <c r="O45" s="144"/>
+      <c r="P45" s="144"/>
       <c r="Q45" s="4" t="s">
         <v>11</v>
       </c>
@@ -3478,12 +3484,14 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
-      <c r="AC45" s="1"/>
-      <c r="AD45" s="1"/>
-      <c r="AE45" s="1"/>
-      <c r="AF45" s="1"/>
-      <c r="AG45" s="1"/>
-      <c r="AH45" s="1"/>
+      <c r="AC45" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD45" s="15"/>
+      <c r="AE45" s="15"/>
+      <c r="AF45" s="15"/>
+      <c r="AG45" s="15"/>
+      <c r="AH45" s="15"/>
       <c r="AI45" s="4" t="s">
         <v>11</v>
       </c>
@@ -3491,51 +3499,51 @@
       <c r="AK45" s="4"/>
       <c r="AL45" s="4"/>
       <c r="AM45" s="4"/>
-      <c r="AN45" s="122"/>
+      <c r="AN45" s="123"/>
     </row>
     <row r="46" spans="1:40" customHeight="1" ht="36.8">
-      <c r="A46" s="104" t="s">
+      <c r="A46" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="B46" s="106"/>
-      <c r="C46" s="106"/>
-      <c r="D46" s="106"/>
-      <c r="E46" s="106"/>
-      <c r="F46" s="106"/>
-      <c r="G46" s="106"/>
-      <c r="H46" s="106"/>
-      <c r="I46" s="106"/>
-      <c r="J46" s="106"/>
-      <c r="K46" s="106"/>
-      <c r="L46" s="106"/>
-      <c r="M46" s="106"/>
-      <c r="N46" s="106"/>
-      <c r="O46" s="106"/>
-      <c r="P46" s="106"/>
-      <c r="Q46" s="106"/>
-      <c r="R46" s="106"/>
-      <c r="S46" s="106"/>
-      <c r="T46" s="106"/>
-      <c r="U46" s="106"/>
-      <c r="V46" s="106"/>
-      <c r="W46" s="106"/>
-      <c r="X46" s="106"/>
-      <c r="Y46" s="106"/>
-      <c r="Z46" s="106"/>
-      <c r="AA46" s="106"/>
-      <c r="AB46" s="106"/>
-      <c r="AC46" s="106"/>
-      <c r="AD46" s="106"/>
-      <c r="AE46" s="106"/>
-      <c r="AF46" s="106"/>
-      <c r="AG46" s="106"/>
-      <c r="AH46" s="106"/>
-      <c r="AI46" s="106"/>
-      <c r="AJ46" s="106"/>
-      <c r="AK46" s="106"/>
-      <c r="AL46" s="106"/>
-      <c r="AM46" s="106"/>
-      <c r="AN46" s="123"/>
+      <c r="B46" s="107"/>
+      <c r="C46" s="107"/>
+      <c r="D46" s="107"/>
+      <c r="E46" s="107"/>
+      <c r="F46" s="107"/>
+      <c r="G46" s="107"/>
+      <c r="H46" s="107"/>
+      <c r="I46" s="107"/>
+      <c r="J46" s="107"/>
+      <c r="K46" s="107"/>
+      <c r="L46" s="107"/>
+      <c r="M46" s="107"/>
+      <c r="N46" s="107"/>
+      <c r="O46" s="107"/>
+      <c r="P46" s="107"/>
+      <c r="Q46" s="107"/>
+      <c r="R46" s="107"/>
+      <c r="S46" s="107"/>
+      <c r="T46" s="107"/>
+      <c r="U46" s="107"/>
+      <c r="V46" s="107"/>
+      <c r="W46" s="107"/>
+      <c r="X46" s="107"/>
+      <c r="Y46" s="107"/>
+      <c r="Z46" s="107"/>
+      <c r="AA46" s="107"/>
+      <c r="AB46" s="107"/>
+      <c r="AC46" s="107"/>
+      <c r="AD46" s="107"/>
+      <c r="AE46" s="107"/>
+      <c r="AF46" s="107"/>
+      <c r="AG46" s="107"/>
+      <c r="AH46" s="107"/>
+      <c r="AI46" s="107"/>
+      <c r="AJ46" s="107"/>
+      <c r="AK46" s="107"/>
+      <c r="AL46" s="107"/>
+      <c r="AM46" s="107"/>
+      <c r="AN46" s="124"/>
     </row>
     <row r="47" spans="1:40" customHeight="1" ht="18">
       <c r="A47" s="1"/>
@@ -3551,37 +3559,37 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
-      <c r="N47" s="90" t="s">
+      <c r="N47" s="91" t="s">
         <v>75</v>
       </c>
-      <c r="O47" s="90"/>
-      <c r="P47" s="90"/>
-      <c r="Q47" s="90"/>
-      <c r="R47" s="90"/>
-      <c r="S47" s="90"/>
-      <c r="T47" s="90"/>
-      <c r="U47" s="90"/>
-      <c r="V47" s="90"/>
-      <c r="W47" s="90"/>
-      <c r="X47" s="90"/>
-      <c r="Y47" s="90"/>
-      <c r="Z47" s="90"/>
-      <c r="AA47" s="90"/>
-      <c r="AB47" s="15" t="s">
+      <c r="O47" s="91"/>
+      <c r="P47" s="91"/>
+      <c r="Q47" s="91"/>
+      <c r="R47" s="91"/>
+      <c r="S47" s="91"/>
+      <c r="T47" s="91"/>
+      <c r="U47" s="91"/>
+      <c r="V47" s="91"/>
+      <c r="W47" s="91"/>
+      <c r="X47" s="91"/>
+      <c r="Y47" s="91"/>
+      <c r="Z47" s="91"/>
+      <c r="AA47" s="91"/>
+      <c r="AB47" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AC47" s="15"/>
-      <c r="AD47" s="15"/>
-      <c r="AE47" s="15"/>
-      <c r="AF47" s="15"/>
-      <c r="AG47" s="15"/>
-      <c r="AH47" s="15"/>
-      <c r="AI47" s="15"/>
-      <c r="AJ47" s="15"/>
-      <c r="AK47" s="15"/>
-      <c r="AL47" s="15"/>
-      <c r="AM47" s="15"/>
-      <c r="AN47" s="15"/>
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="16"/>
+      <c r="AF47" s="16"/>
+      <c r="AG47" s="16"/>
+      <c r="AH47" s="16"/>
+      <c r="AI47" s="16"/>
+      <c r="AJ47" s="16"/>
+      <c r="AK47" s="16"/>
+      <c r="AL47" s="16"/>
+      <c r="AM47" s="16"/>
+      <c r="AN47" s="16"/>
     </row>
   </sheetData>
   <mergeCells>
